--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -5214,10 +5214,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119568651</v>
+        <v>119568829</v>
       </c>
       <c r="B42" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5230,24 +5230,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5257,13 +5261,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481001</v>
+        <v>480735</v>
       </c>
       <c r="R42" t="n">
-        <v>6787625</v>
+        <v>6787658</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5293,11 +5297,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>flera</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5325,10 +5324,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119568829</v>
+        <v>119566096</v>
       </c>
       <c r="B43" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,44 +5340,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480735</v>
+        <v>480980</v>
       </c>
       <c r="R43" t="n">
-        <v>6787658</v>
+        <v>6787594</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5405,37 +5401,46 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119566096</v>
+        <v>119568651</v>
       </c>
       <c r="B44" t="n">
         <v>91884</v>
@@ -5468,24 +5473,23 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480980</v>
+        <v>481001</v>
       </c>
       <c r="R44" t="n">
-        <v>6787594</v>
+        <v>6787625</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5512,19 +5516,14 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:43</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>flera</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5533,18 +5532,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -6224,7 +6224,7 @@
         <v>120837852</v>
       </c>
       <c r="B51" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6333,6 +6333,2156 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121972890</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92032</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>480809</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6787568</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121972907</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92016</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>480936</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6787692</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121972892</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92032</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>480843</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6787540</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121972920</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>480994</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6787675</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121972916</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>480915</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6787807</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121972897</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92020</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>481022</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6787739</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>121972913</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78353</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>480935</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6787807</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>121972898</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92020</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>480829</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6787731</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>121972911</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91996</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>480843</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6787540</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121972921</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>480761</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6787650</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>121972885</v>
+      </c>
+      <c r="B62" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>481124</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6787703</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121972884</v>
+      </c>
+      <c r="B63" t="n">
+        <v>86262</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vaxspindling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cortinarius pinophilus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>480986</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6787836</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121972919</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>480773</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6787678</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121972901</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92020</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>480745</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6787692</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>121972889</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92032</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>481131</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6787677</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>121972922</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>480796</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6787645</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>121972918</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>480812</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6787702</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121972883</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78650</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>185</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>480860</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6787521</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>121972917</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>480797</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6787722</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>121972912</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92201</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>480966</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6787791</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>121972915</v>
+      </c>
+      <c r="B72" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>480914</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6787844</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -6335,10 +6335,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121972890</v>
+        <v>121972915</v>
       </c>
       <c r="B52" t="n">
-        <v>92032</v>
+        <v>92004</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6347,38 +6347,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480809</v>
+        <v>480914</v>
       </c>
       <c r="R52" t="n">
-        <v>6787568</v>
+        <v>6787844</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6437,10 +6437,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121972907</v>
+        <v>121972897</v>
       </c>
       <c r="B53" t="n">
-        <v>92016</v>
+        <v>92020</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6449,25 +6449,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480936</v>
+        <v>481022</v>
       </c>
       <c r="R53" t="n">
-        <v>6787692</v>
+        <v>6787739</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121972892</v>
+        <v>121972917</v>
       </c>
       <c r="B54" t="n">
-        <v>92032</v>
+        <v>92004</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6551,38 +6551,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480843</v>
+        <v>480797</v>
       </c>
       <c r="R54" t="n">
-        <v>6787540</v>
+        <v>6787722</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6641,10 +6641,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121972920</v>
+        <v>121972883</v>
       </c>
       <c r="B55" t="n">
-        <v>92004</v>
+        <v>78650</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6653,38 +6653,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480994</v>
+        <v>480860</v>
       </c>
       <c r="R55" t="n">
-        <v>6787675</v>
+        <v>6787521</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6845,7 +6845,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121972897</v>
+        <v>121972901</v>
       </c>
       <c r="B57" t="n">
         <v>92020</v>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481022</v>
+        <v>480745</v>
       </c>
       <c r="R57" t="n">
-        <v>6787739</v>
+        <v>6787692</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6947,10 +6947,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121972913</v>
+        <v>121972890</v>
       </c>
       <c r="B58" t="n">
-        <v>78353</v>
+        <v>92032</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6963,34 +6963,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480935</v>
+        <v>480809</v>
       </c>
       <c r="R58" t="n">
-        <v>6787807</v>
+        <v>6787568</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7049,10 +7049,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121972898</v>
+        <v>121972922</v>
       </c>
       <c r="B59" t="n">
-        <v>92020</v>
+        <v>92004</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7061,25 +7061,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480829</v>
+        <v>480796</v>
       </c>
       <c r="R59" t="n">
-        <v>6787731</v>
+        <v>6787645</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7151,10 +7151,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121972911</v>
+        <v>121972907</v>
       </c>
       <c r="B60" t="n">
-        <v>91996</v>
+        <v>92016</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7163,38 +7163,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480843</v>
+        <v>480936</v>
       </c>
       <c r="R60" t="n">
-        <v>6787540</v>
+        <v>6787692</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7253,7 +7253,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121972921</v>
+        <v>121972918</v>
       </c>
       <c r="B61" t="n">
         <v>92004</v>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480761</v>
+        <v>480812</v>
       </c>
       <c r="R61" t="n">
-        <v>6787650</v>
+        <v>6787702</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7355,10 +7355,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121972885</v>
+        <v>121972911</v>
       </c>
       <c r="B62" t="n">
-        <v>90728</v>
+        <v>91996</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,34 +7371,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481124</v>
+        <v>480843</v>
       </c>
       <c r="R62" t="n">
-        <v>6787703</v>
+        <v>6787540</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121972884</v>
+        <v>121972921</v>
       </c>
       <c r="B63" t="n">
-        <v>86262</v>
+        <v>92004</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7469,41 +7469,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480986</v>
+        <v>480761</v>
       </c>
       <c r="R63" t="n">
-        <v>6787836</v>
+        <v>6787650</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7536,11 +7533,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7567,10 +7559,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121972919</v>
+        <v>121972913</v>
       </c>
       <c r="B64" t="n">
-        <v>92004</v>
+        <v>78353</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7579,25 +7571,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7607,10 +7599,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480773</v>
+        <v>480935</v>
       </c>
       <c r="R64" t="n">
-        <v>6787678</v>
+        <v>6787807</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7669,10 +7661,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121972901</v>
+        <v>121972885</v>
       </c>
       <c r="B65" t="n">
-        <v>92020</v>
+        <v>90728</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7685,21 +7677,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7709,10 +7701,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480745</v>
+        <v>481124</v>
       </c>
       <c r="R65" t="n">
-        <v>6787692</v>
+        <v>6787703</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7771,10 +7763,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121972889</v>
+        <v>121972920</v>
       </c>
       <c r="B66" t="n">
-        <v>92032</v>
+        <v>92004</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7783,25 +7775,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7811,10 +7803,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481131</v>
+        <v>480994</v>
       </c>
       <c r="R66" t="n">
-        <v>6787677</v>
+        <v>6787675</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7873,10 +7865,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121972922</v>
+        <v>121972912</v>
       </c>
       <c r="B67" t="n">
-        <v>92004</v>
+        <v>92201</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7885,25 +7877,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7913,10 +7905,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480796</v>
+        <v>480966</v>
       </c>
       <c r="R67" t="n">
-        <v>6787645</v>
+        <v>6787791</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7975,7 +7967,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121972918</v>
+        <v>121972919</v>
       </c>
       <c r="B68" t="n">
         <v>92004</v>
@@ -8015,10 +8007,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480812</v>
+        <v>480773</v>
       </c>
       <c r="R68" t="n">
-        <v>6787702</v>
+        <v>6787678</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8077,10 +8069,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121972883</v>
+        <v>121972889</v>
       </c>
       <c r="B69" t="n">
-        <v>78650</v>
+        <v>92032</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8093,34 +8085,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480860</v>
+        <v>481131</v>
       </c>
       <c r="R69" t="n">
-        <v>6787521</v>
+        <v>6787677</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8179,10 +8171,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121972917</v>
+        <v>121972884</v>
       </c>
       <c r="B70" t="n">
-        <v>92004</v>
+        <v>86262</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8191,38 +8183,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480797</v>
+        <v>480986</v>
       </c>
       <c r="R70" t="n">
-        <v>6787722</v>
+        <v>6787836</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8255,6 +8250,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8281,10 +8281,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121972912</v>
+        <v>121972892</v>
       </c>
       <c r="B71" t="n">
-        <v>92201</v>
+        <v>92032</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8297,34 +8297,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480966</v>
+        <v>480843</v>
       </c>
       <c r="R71" t="n">
-        <v>6787791</v>
+        <v>6787540</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121972915</v>
+        <v>121972898</v>
       </c>
       <c r="B72" t="n">
-        <v>92004</v>
+        <v>92020</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,25 +8395,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480914</v>
+        <v>480829</v>
       </c>
       <c r="R72" t="n">
-        <v>6787844</v>
+        <v>6787731</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -6335,10 +6335,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121972915</v>
+        <v>121972916</v>
       </c>
       <c r="B52" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480914</v>
+        <v>480915</v>
       </c>
       <c r="R52" t="n">
-        <v>6787844</v>
+        <v>6787807</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6437,10 +6437,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121972897</v>
+        <v>121972898</v>
       </c>
       <c r="B53" t="n">
-        <v>92020</v>
+        <v>92034</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481022</v>
+        <v>480829</v>
       </c>
       <c r="R53" t="n">
-        <v>6787739</v>
+        <v>6787731</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121972917</v>
+        <v>121972890</v>
       </c>
       <c r="B54" t="n">
-        <v>92004</v>
+        <v>92046</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6551,38 +6551,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480797</v>
+        <v>480809</v>
       </c>
       <c r="R54" t="n">
-        <v>6787722</v>
+        <v>6787568</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6641,10 +6641,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121972883</v>
+        <v>121972922</v>
       </c>
       <c r="B55" t="n">
-        <v>78650</v>
+        <v>92018</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6653,38 +6653,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480860</v>
+        <v>480796</v>
       </c>
       <c r="R55" t="n">
-        <v>6787521</v>
+        <v>6787645</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6743,10 +6743,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121972916</v>
+        <v>121972883</v>
       </c>
       <c r="B56" t="n">
-        <v>92004</v>
+        <v>78663</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6755,38 +6755,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480915</v>
+        <v>480860</v>
       </c>
       <c r="R56" t="n">
-        <v>6787807</v>
+        <v>6787521</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121972901</v>
+        <v>121972884</v>
       </c>
       <c r="B57" t="n">
-        <v>92020</v>
+        <v>86276</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6861,34 +6861,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>3690</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480745</v>
+        <v>480986</v>
       </c>
       <c r="R57" t="n">
-        <v>6787692</v>
+        <v>6787836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6921,6 +6924,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6947,10 +6955,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121972890</v>
+        <v>121972913</v>
       </c>
       <c r="B58" t="n">
-        <v>92032</v>
+        <v>78366</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6963,34 +6971,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480809</v>
+        <v>480935</v>
       </c>
       <c r="R58" t="n">
-        <v>6787568</v>
+        <v>6787807</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7049,10 +7057,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121972922</v>
+        <v>121972915</v>
       </c>
       <c r="B59" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7089,10 +7097,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480796</v>
+        <v>480914</v>
       </c>
       <c r="R59" t="n">
-        <v>6787645</v>
+        <v>6787844</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7151,10 +7159,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121972907</v>
+        <v>121972897</v>
       </c>
       <c r="B60" t="n">
-        <v>92016</v>
+        <v>92034</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7163,25 +7171,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7191,10 +7199,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480936</v>
+        <v>481022</v>
       </c>
       <c r="R60" t="n">
-        <v>6787692</v>
+        <v>6787739</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7253,10 +7261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121972918</v>
+        <v>121972920</v>
       </c>
       <c r="B61" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7293,10 +7301,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480812</v>
+        <v>480994</v>
       </c>
       <c r="R61" t="n">
-        <v>6787702</v>
+        <v>6787675</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7355,10 +7363,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121972911</v>
+        <v>121972885</v>
       </c>
       <c r="B62" t="n">
-        <v>91996</v>
+        <v>90742</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,34 +7379,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480843</v>
+        <v>481124</v>
       </c>
       <c r="R62" t="n">
-        <v>6787540</v>
+        <v>6787703</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7460,7 +7468,7 @@
         <v>121972921</v>
       </c>
       <c r="B63" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7559,10 +7567,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121972913</v>
+        <v>121972901</v>
       </c>
       <c r="B64" t="n">
-        <v>78353</v>
+        <v>92034</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7575,21 +7583,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7599,10 +7607,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480935</v>
+        <v>480745</v>
       </c>
       <c r="R64" t="n">
-        <v>6787807</v>
+        <v>6787692</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7661,10 +7669,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121972885</v>
+        <v>121972907</v>
       </c>
       <c r="B65" t="n">
-        <v>90728</v>
+        <v>92030</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7673,25 +7681,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7701,10 +7709,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481124</v>
+        <v>480936</v>
       </c>
       <c r="R65" t="n">
-        <v>6787703</v>
+        <v>6787692</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7763,10 +7771,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121972920</v>
+        <v>121972911</v>
       </c>
       <c r="B66" t="n">
-        <v>92004</v>
+        <v>92010</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7775,38 +7783,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480994</v>
+        <v>480843</v>
       </c>
       <c r="R66" t="n">
-        <v>6787675</v>
+        <v>6787540</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7865,10 +7873,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121972912</v>
+        <v>121972889</v>
       </c>
       <c r="B67" t="n">
-        <v>92201</v>
+        <v>92046</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7881,21 +7889,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7905,10 +7913,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480966</v>
+        <v>481131</v>
       </c>
       <c r="R67" t="n">
-        <v>6787791</v>
+        <v>6787677</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7967,10 +7975,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121972919</v>
+        <v>121972917</v>
       </c>
       <c r="B68" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8007,10 +8015,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480773</v>
+        <v>480797</v>
       </c>
       <c r="R68" t="n">
-        <v>6787678</v>
+        <v>6787722</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8069,10 +8077,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121972889</v>
+        <v>121972918</v>
       </c>
       <c r="B69" t="n">
-        <v>92032</v>
+        <v>92018</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8081,25 +8089,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8109,10 +8117,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481131</v>
+        <v>480812</v>
       </c>
       <c r="R69" t="n">
-        <v>6787677</v>
+        <v>6787702</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8171,10 +8179,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121972884</v>
+        <v>121972912</v>
       </c>
       <c r="B70" t="n">
-        <v>86262</v>
+        <v>92215</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,37 +8195,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3690</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480986</v>
+        <v>480966</v>
       </c>
       <c r="R70" t="n">
-        <v>6787836</v>
+        <v>6787791</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8250,11 +8255,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8284,7 +8284,7 @@
         <v>121972892</v>
       </c>
       <c r="B71" t="n">
-        <v>92032</v>
+        <v>92046</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121972898</v>
+        <v>121972919</v>
       </c>
       <c r="B72" t="n">
-        <v>92020</v>
+        <v>92018</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,25 +8395,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480829</v>
+        <v>480773</v>
       </c>
       <c r="R72" t="n">
-        <v>6787731</v>
+        <v>6787678</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -7363,10 +7363,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121972885</v>
+        <v>121972921</v>
       </c>
       <c r="B62" t="n">
-        <v>90742</v>
+        <v>92018</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7375,25 +7375,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481124</v>
+        <v>480761</v>
       </c>
       <c r="R62" t="n">
-        <v>6787703</v>
+        <v>6787650</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7465,10 +7465,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121972921</v>
+        <v>121972885</v>
       </c>
       <c r="B63" t="n">
-        <v>92018</v>
+        <v>90742</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7477,25 +7477,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480761</v>
+        <v>481124</v>
       </c>
       <c r="R63" t="n">
-        <v>6787650</v>
+        <v>6787703</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -6335,10 +6335,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121972913</v>
+        <v>121972898</v>
       </c>
       <c r="B52" t="n">
-        <v>78382</v>
+        <v>92071</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6351,21 +6351,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480935</v>
+        <v>480829</v>
       </c>
       <c r="R52" t="n">
-        <v>6787807</v>
+        <v>6787731</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6437,7 +6437,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121972922</v>
+        <v>121972915</v>
       </c>
       <c r="B53" t="n">
         <v>92055</v>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480796</v>
+        <v>480914</v>
       </c>
       <c r="R53" t="n">
-        <v>6787645</v>
+        <v>6787844</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121972897</v>
+        <v>121972889</v>
       </c>
       <c r="B54" t="n">
-        <v>92071</v>
+        <v>92083</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6555,21 +6555,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481022</v>
+        <v>481131</v>
       </c>
       <c r="R54" t="n">
-        <v>6787739</v>
+        <v>6787677</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6641,10 +6641,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121972921</v>
+        <v>121972901</v>
       </c>
       <c r="B55" t="n">
-        <v>92055</v>
+        <v>92071</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6653,25 +6653,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480761</v>
+        <v>480745</v>
       </c>
       <c r="R55" t="n">
-        <v>6787650</v>
+        <v>6787692</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6743,10 +6743,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121972911</v>
+        <v>121972921</v>
       </c>
       <c r="B56" t="n">
-        <v>92047</v>
+        <v>92055</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6755,38 +6755,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480843</v>
+        <v>480761</v>
       </c>
       <c r="R56" t="n">
-        <v>6787540</v>
+        <v>6787650</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121972898</v>
+        <v>121972884</v>
       </c>
       <c r="B57" t="n">
-        <v>92071</v>
+        <v>86313</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6861,34 +6861,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>3690</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480829</v>
+        <v>480986</v>
       </c>
       <c r="R57" t="n">
-        <v>6787731</v>
+        <v>6787836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6921,6 +6924,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6947,10 +6955,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121972889</v>
+        <v>121972913</v>
       </c>
       <c r="B58" t="n">
-        <v>92083</v>
+        <v>78382</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6963,21 +6971,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6987,10 +6995,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481131</v>
+        <v>480935</v>
       </c>
       <c r="R58" t="n">
-        <v>6787677</v>
+        <v>6787807</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7049,7 +7057,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121972915</v>
+        <v>121972916</v>
       </c>
       <c r="B59" t="n">
         <v>92055</v>
@@ -7089,10 +7097,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480914</v>
+        <v>480915</v>
       </c>
       <c r="R59" t="n">
-        <v>6787844</v>
+        <v>6787807</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7151,7 +7159,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121972917</v>
+        <v>121972920</v>
       </c>
       <c r="B60" t="n">
         <v>92055</v>
@@ -7191,10 +7199,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480797</v>
+        <v>480994</v>
       </c>
       <c r="R60" t="n">
-        <v>6787722</v>
+        <v>6787675</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7253,10 +7261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121972918</v>
+        <v>121972883</v>
       </c>
       <c r="B61" t="n">
-        <v>92055</v>
+        <v>78679</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7265,38 +7273,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480812</v>
+        <v>480860</v>
       </c>
       <c r="R61" t="n">
-        <v>6787702</v>
+        <v>6787521</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7355,10 +7363,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121972892</v>
+        <v>121972918</v>
       </c>
       <c r="B62" t="n">
-        <v>92083</v>
+        <v>92055</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7367,38 +7375,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480843</v>
+        <v>480812</v>
       </c>
       <c r="R62" t="n">
-        <v>6787540</v>
+        <v>6787702</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7457,10 +7465,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121972919</v>
+        <v>121972911</v>
       </c>
       <c r="B63" t="n">
-        <v>92055</v>
+        <v>92047</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7469,38 +7477,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480773</v>
+        <v>480843</v>
       </c>
       <c r="R63" t="n">
-        <v>6787678</v>
+        <v>6787540</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7559,10 +7567,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121972912</v>
+        <v>121972897</v>
       </c>
       <c r="B64" t="n">
-        <v>92252</v>
+        <v>92071</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7575,21 +7583,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7599,10 +7607,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480966</v>
+        <v>481022</v>
       </c>
       <c r="R64" t="n">
-        <v>6787791</v>
+        <v>6787739</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7661,10 +7669,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121972883</v>
+        <v>121972885</v>
       </c>
       <c r="B65" t="n">
-        <v>78679</v>
+        <v>90779</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7677,34 +7685,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480860</v>
+        <v>481124</v>
       </c>
       <c r="R65" t="n">
-        <v>6787521</v>
+        <v>6787703</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7763,10 +7771,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121972916</v>
+        <v>121972912</v>
       </c>
       <c r="B66" t="n">
-        <v>92055</v>
+        <v>92252</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7775,25 +7783,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7803,10 +7811,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480915</v>
+        <v>480966</v>
       </c>
       <c r="R66" t="n">
-        <v>6787807</v>
+        <v>6787791</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7865,10 +7873,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121972885</v>
+        <v>121972919</v>
       </c>
       <c r="B67" t="n">
-        <v>90779</v>
+        <v>92055</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7877,25 +7885,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7905,10 +7913,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481124</v>
+        <v>480773</v>
       </c>
       <c r="R67" t="n">
-        <v>6787703</v>
+        <v>6787678</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7967,10 +7975,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121972901</v>
+        <v>121972917</v>
       </c>
       <c r="B68" t="n">
-        <v>92071</v>
+        <v>92055</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7979,25 +7987,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8007,10 +8015,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480745</v>
+        <v>480797</v>
       </c>
       <c r="R68" t="n">
-        <v>6787692</v>
+        <v>6787722</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8069,10 +8077,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121972907</v>
+        <v>121972922</v>
       </c>
       <c r="B69" t="n">
-        <v>92067</v>
+        <v>92055</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,21 +8093,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8109,10 +8117,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480936</v>
+        <v>480796</v>
       </c>
       <c r="R69" t="n">
-        <v>6787692</v>
+        <v>6787645</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8171,10 +8179,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121972890</v>
+        <v>121972907</v>
       </c>
       <c r="B70" t="n">
-        <v>92083</v>
+        <v>92067</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8183,38 +8191,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480809</v>
+        <v>480936</v>
       </c>
       <c r="R70" t="n">
-        <v>6787568</v>
+        <v>6787692</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8273,10 +8281,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121972884</v>
+        <v>121972890</v>
       </c>
       <c r="B71" t="n">
-        <v>86313</v>
+        <v>92083</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8289,37 +8297,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3690</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480986</v>
+        <v>480809</v>
       </c>
       <c r="R71" t="n">
-        <v>6787836</v>
+        <v>6787568</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8352,11 +8357,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8383,10 +8383,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121972920</v>
+        <v>121972892</v>
       </c>
       <c r="B72" t="n">
-        <v>92055</v>
+        <v>92083</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,38 +8395,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480994</v>
+        <v>480843</v>
       </c>
       <c r="R72" t="n">
-        <v>6787675</v>
+        <v>6787540</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -6335,10 +6335,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121972898</v>
+        <v>121972919</v>
       </c>
       <c r="B52" t="n">
-        <v>92071</v>
+        <v>92065</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6347,25 +6347,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480829</v>
+        <v>480773</v>
       </c>
       <c r="R52" t="n">
-        <v>6787731</v>
+        <v>6787678</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6437,10 +6437,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121972915</v>
+        <v>121972918</v>
       </c>
       <c r="B53" t="n">
-        <v>92055</v>
+        <v>92065</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480914</v>
+        <v>480812</v>
       </c>
       <c r="R53" t="n">
-        <v>6787844</v>
+        <v>6787702</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121972889</v>
+        <v>121972901</v>
       </c>
       <c r="B54" t="n">
-        <v>92083</v>
+        <v>92081</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6555,21 +6555,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481131</v>
+        <v>480745</v>
       </c>
       <c r="R54" t="n">
-        <v>6787677</v>
+        <v>6787692</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6641,10 +6641,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121972901</v>
+        <v>121972913</v>
       </c>
       <c r="B55" t="n">
-        <v>92071</v>
+        <v>78383</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6657,21 +6657,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480745</v>
+        <v>480935</v>
       </c>
       <c r="R55" t="n">
-        <v>6787692</v>
+        <v>6787807</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6743,10 +6743,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121972921</v>
+        <v>121972912</v>
       </c>
       <c r="B56" t="n">
-        <v>92055</v>
+        <v>92262</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6755,25 +6755,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6783,10 +6783,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480761</v>
+        <v>480966</v>
       </c>
       <c r="R56" t="n">
-        <v>6787650</v>
+        <v>6787791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121972884</v>
+        <v>121972897</v>
       </c>
       <c r="B57" t="n">
-        <v>86313</v>
+        <v>92081</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6861,37 +6861,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480986</v>
+        <v>481022</v>
       </c>
       <c r="R57" t="n">
-        <v>6787836</v>
+        <v>6787739</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6924,11 +6921,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6955,10 +6947,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121972913</v>
+        <v>121972915</v>
       </c>
       <c r="B58" t="n">
-        <v>78382</v>
+        <v>92065</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,25 +6959,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6995,10 +6987,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480935</v>
+        <v>480914</v>
       </c>
       <c r="R58" t="n">
-        <v>6787807</v>
+        <v>6787844</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7057,10 +7049,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121972916</v>
+        <v>121972889</v>
       </c>
       <c r="B59" t="n">
-        <v>92055</v>
+        <v>92093</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7069,25 +7061,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7097,10 +7089,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480915</v>
+        <v>481131</v>
       </c>
       <c r="R59" t="n">
-        <v>6787807</v>
+        <v>6787677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7159,10 +7151,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121972920</v>
+        <v>121972884</v>
       </c>
       <c r="B60" t="n">
-        <v>92055</v>
+        <v>86314</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7171,38 +7163,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480994</v>
+        <v>480986</v>
       </c>
       <c r="R60" t="n">
-        <v>6787675</v>
+        <v>6787836</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7235,6 +7230,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7261,10 +7261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121972883</v>
+        <v>121972920</v>
       </c>
       <c r="B61" t="n">
-        <v>78679</v>
+        <v>92065</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,38 +7273,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480860</v>
+        <v>480994</v>
       </c>
       <c r="R61" t="n">
-        <v>6787521</v>
+        <v>6787675</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7363,10 +7363,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121972918</v>
+        <v>121972890</v>
       </c>
       <c r="B62" t="n">
-        <v>92055</v>
+        <v>92093</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7375,38 +7375,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480812</v>
+        <v>480809</v>
       </c>
       <c r="R62" t="n">
-        <v>6787702</v>
+        <v>6787568</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7465,10 +7465,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121972911</v>
+        <v>121972917</v>
       </c>
       <c r="B63" t="n">
-        <v>92047</v>
+        <v>92065</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7477,38 +7477,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480843</v>
+        <v>480797</v>
       </c>
       <c r="R63" t="n">
-        <v>6787540</v>
+        <v>6787722</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7567,10 +7567,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121972897</v>
+        <v>121972922</v>
       </c>
       <c r="B64" t="n">
-        <v>92071</v>
+        <v>92065</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7579,25 +7579,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481022</v>
+        <v>480796</v>
       </c>
       <c r="R64" t="n">
-        <v>6787739</v>
+        <v>6787645</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7669,10 +7669,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121972885</v>
+        <v>121972883</v>
       </c>
       <c r="B65" t="n">
-        <v>90779</v>
+        <v>78680</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7685,34 +7685,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481124</v>
+        <v>480860</v>
       </c>
       <c r="R65" t="n">
-        <v>6787703</v>
+        <v>6787521</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7771,10 +7771,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121972912</v>
+        <v>121972907</v>
       </c>
       <c r="B66" t="n">
-        <v>92252</v>
+        <v>92077</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7783,25 +7783,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2079</v>
+        <v>4366</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480966</v>
+        <v>480936</v>
       </c>
       <c r="R66" t="n">
-        <v>6787791</v>
+        <v>6787692</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7873,10 +7873,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121972919</v>
+        <v>121972911</v>
       </c>
       <c r="B67" t="n">
-        <v>92055</v>
+        <v>92057</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7885,38 +7885,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480773</v>
+        <v>480843</v>
       </c>
       <c r="R67" t="n">
-        <v>6787678</v>
+        <v>6787540</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7975,10 +7975,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121972917</v>
+        <v>121972921</v>
       </c>
       <c r="B68" t="n">
-        <v>92055</v>
+        <v>92065</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480797</v>
+        <v>480761</v>
       </c>
       <c r="R68" t="n">
-        <v>6787722</v>
+        <v>6787650</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8077,10 +8077,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121972922</v>
+        <v>121972885</v>
       </c>
       <c r="B69" t="n">
-        <v>92055</v>
+        <v>90789</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8089,25 +8089,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480796</v>
+        <v>481124</v>
       </c>
       <c r="R69" t="n">
-        <v>6787645</v>
+        <v>6787703</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8179,10 +8179,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121972907</v>
+        <v>121972898</v>
       </c>
       <c r="B70" t="n">
-        <v>92067</v>
+        <v>92081</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8191,25 +8191,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480936</v>
+        <v>480829</v>
       </c>
       <c r="R70" t="n">
-        <v>6787692</v>
+        <v>6787731</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8281,10 +8281,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121972890</v>
+        <v>121972892</v>
       </c>
       <c r="B71" t="n">
-        <v>92083</v>
+        <v>92093</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480809</v>
+        <v>480843</v>
       </c>
       <c r="R71" t="n">
-        <v>6787568</v>
+        <v>6787540</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121972892</v>
+        <v>121972916</v>
       </c>
       <c r="B72" t="n">
-        <v>92083</v>
+        <v>92065</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,38 +8395,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480843</v>
+        <v>480915</v>
       </c>
       <c r="R72" t="n">
-        <v>6787540</v>
+        <v>6787807</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -6335,10 +6335,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121972919</v>
+        <v>121972885</v>
       </c>
       <c r="B52" t="n">
-        <v>92065</v>
+        <v>90789</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6347,25 +6347,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480773</v>
+        <v>481124</v>
       </c>
       <c r="R52" t="n">
-        <v>6787678</v>
+        <v>6787703</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6437,7 +6437,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121972918</v>
+        <v>121972916</v>
       </c>
       <c r="B53" t="n">
         <v>92065</v>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480812</v>
+        <v>480915</v>
       </c>
       <c r="R53" t="n">
-        <v>6787702</v>
+        <v>6787807</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121972901</v>
+        <v>121972919</v>
       </c>
       <c r="B54" t="n">
-        <v>92081</v>
+        <v>92065</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6551,25 +6551,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480745</v>
+        <v>480773</v>
       </c>
       <c r="R54" t="n">
-        <v>6787692</v>
+        <v>6787678</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6641,10 +6641,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121972913</v>
+        <v>121972922</v>
       </c>
       <c r="B55" t="n">
-        <v>78383</v>
+        <v>92065</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6653,25 +6653,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480935</v>
+        <v>480796</v>
       </c>
       <c r="R55" t="n">
-        <v>6787807</v>
+        <v>6787645</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6743,10 +6743,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121972912</v>
+        <v>121972915</v>
       </c>
       <c r="B56" t="n">
-        <v>92262</v>
+        <v>92065</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6755,25 +6755,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6783,10 +6783,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480966</v>
+        <v>480914</v>
       </c>
       <c r="R56" t="n">
-        <v>6787791</v>
+        <v>6787844</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121972897</v>
+        <v>121972917</v>
       </c>
       <c r="B57" t="n">
-        <v>92081</v>
+        <v>92065</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6857,25 +6857,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481022</v>
+        <v>480797</v>
       </c>
       <c r="R57" t="n">
-        <v>6787739</v>
+        <v>6787722</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6947,10 +6947,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121972915</v>
+        <v>121972898</v>
       </c>
       <c r="B58" t="n">
-        <v>92065</v>
+        <v>92081</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6959,25 +6959,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480914</v>
+        <v>480829</v>
       </c>
       <c r="R58" t="n">
-        <v>6787844</v>
+        <v>6787731</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7049,10 +7049,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121972889</v>
+        <v>121972901</v>
       </c>
       <c r="B59" t="n">
-        <v>92093</v>
+        <v>92081</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7065,21 +7065,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481131</v>
+        <v>480745</v>
       </c>
       <c r="R59" t="n">
-        <v>6787677</v>
+        <v>6787692</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7151,10 +7151,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121972884</v>
+        <v>121972913</v>
       </c>
       <c r="B60" t="n">
-        <v>86314</v>
+        <v>78383</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7167,37 +7167,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3690</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480986</v>
+        <v>480935</v>
       </c>
       <c r="R60" t="n">
-        <v>6787836</v>
+        <v>6787807</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7230,11 +7227,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7363,7 +7355,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121972890</v>
+        <v>121972889</v>
       </c>
       <c r="B62" t="n">
         <v>92093</v>
@@ -7399,14 +7391,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480809</v>
+        <v>481131</v>
       </c>
       <c r="R62" t="n">
-        <v>6787568</v>
+        <v>6787677</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7465,7 +7457,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121972917</v>
+        <v>121972918</v>
       </c>
       <c r="B63" t="n">
         <v>92065</v>
@@ -7505,10 +7497,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480797</v>
+        <v>480812</v>
       </c>
       <c r="R63" t="n">
-        <v>6787722</v>
+        <v>6787702</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7567,10 +7559,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121972922</v>
+        <v>121972911</v>
       </c>
       <c r="B64" t="n">
-        <v>92065</v>
+        <v>92057</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7579,38 +7571,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480796</v>
+        <v>480843</v>
       </c>
       <c r="R64" t="n">
-        <v>6787645</v>
+        <v>6787540</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7669,10 +7661,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121972883</v>
+        <v>121972884</v>
       </c>
       <c r="B65" t="n">
-        <v>78680</v>
+        <v>86314</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7685,34 +7677,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>3690</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480860</v>
+        <v>480986</v>
       </c>
       <c r="R65" t="n">
-        <v>6787521</v>
+        <v>6787836</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7745,6 +7740,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7873,10 +7873,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121972911</v>
+        <v>121972890</v>
       </c>
       <c r="B67" t="n">
-        <v>92057</v>
+        <v>92093</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7889,21 +7889,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480843</v>
+        <v>480809</v>
       </c>
       <c r="R67" t="n">
-        <v>6787540</v>
+        <v>6787568</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7975,10 +7975,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121972921</v>
+        <v>121972883</v>
       </c>
       <c r="B68" t="n">
-        <v>92065</v>
+        <v>78680</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,38 +7987,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480761</v>
+        <v>480860</v>
       </c>
       <c r="R68" t="n">
-        <v>6787650</v>
+        <v>6787521</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8077,10 +8077,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121972885</v>
+        <v>121972897</v>
       </c>
       <c r="B69" t="n">
-        <v>90789</v>
+        <v>92081</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8093,21 +8093,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481124</v>
+        <v>481022</v>
       </c>
       <c r="R69" t="n">
-        <v>6787703</v>
+        <v>6787739</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8179,10 +8179,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121972898</v>
+        <v>121972892</v>
       </c>
       <c r="B70" t="n">
-        <v>92081</v>
+        <v>92093</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8195,34 +8195,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480829</v>
+        <v>480843</v>
       </c>
       <c r="R70" t="n">
-        <v>6787731</v>
+        <v>6787540</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8281,10 +8281,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121972892</v>
+        <v>121972921</v>
       </c>
       <c r="B71" t="n">
-        <v>92093</v>
+        <v>92065</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8293,38 +8293,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480843</v>
+        <v>480761</v>
       </c>
       <c r="R71" t="n">
-        <v>6787540</v>
+        <v>6787650</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121972916</v>
+        <v>121972912</v>
       </c>
       <c r="B72" t="n">
-        <v>92065</v>
+        <v>92262</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,25 +8395,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480915</v>
+        <v>480966</v>
       </c>
       <c r="R72" t="n">
-        <v>6787807</v>
+        <v>6787791</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -6335,10 +6335,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121972885</v>
+        <v>121972921</v>
       </c>
       <c r="B52" t="n">
-        <v>90789</v>
+        <v>92077</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6347,25 +6347,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481124</v>
+        <v>480761</v>
       </c>
       <c r="R52" t="n">
-        <v>6787703</v>
+        <v>6787650</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6437,10 +6437,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121972916</v>
+        <v>121972884</v>
       </c>
       <c r="B53" t="n">
-        <v>92065</v>
+        <v>86321</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6449,38 +6449,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480915</v>
+        <v>480986</v>
       </c>
       <c r="R53" t="n">
-        <v>6787807</v>
+        <v>6787836</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,6 +6516,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6539,10 +6547,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121972919</v>
+        <v>121972897</v>
       </c>
       <c r="B54" t="n">
-        <v>92065</v>
+        <v>92093</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6551,25 +6559,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6579,10 +6587,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480773</v>
+        <v>481022</v>
       </c>
       <c r="R54" t="n">
-        <v>6787678</v>
+        <v>6787739</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6641,10 +6649,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121972922</v>
+        <v>121972892</v>
       </c>
       <c r="B55" t="n">
-        <v>92065</v>
+        <v>92105</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6653,38 +6661,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480796</v>
+        <v>480843</v>
       </c>
       <c r="R55" t="n">
-        <v>6787645</v>
+        <v>6787540</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6743,10 +6751,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121972915</v>
+        <v>121972922</v>
       </c>
       <c r="B56" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6783,10 +6791,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480914</v>
+        <v>480796</v>
       </c>
       <c r="R56" t="n">
-        <v>6787844</v>
+        <v>6787645</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6845,10 +6853,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121972917</v>
+        <v>121972920</v>
       </c>
       <c r="B57" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6885,10 +6893,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480797</v>
+        <v>480994</v>
       </c>
       <c r="R57" t="n">
-        <v>6787722</v>
+        <v>6787675</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6947,10 +6955,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121972898</v>
+        <v>121972889</v>
       </c>
       <c r="B58" t="n">
-        <v>92081</v>
+        <v>92105</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6963,21 +6971,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6987,10 +6995,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480829</v>
+        <v>481131</v>
       </c>
       <c r="R58" t="n">
-        <v>6787731</v>
+        <v>6787677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7049,10 +7057,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121972901</v>
+        <v>121972919</v>
       </c>
       <c r="B59" t="n">
-        <v>92081</v>
+        <v>92077</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7061,25 +7069,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7089,10 +7097,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480745</v>
+        <v>480773</v>
       </c>
       <c r="R59" t="n">
-        <v>6787692</v>
+        <v>6787678</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7151,10 +7159,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121972913</v>
+        <v>121972915</v>
       </c>
       <c r="B60" t="n">
-        <v>78383</v>
+        <v>92077</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7163,25 +7171,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7191,10 +7199,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480935</v>
+        <v>480914</v>
       </c>
       <c r="R60" t="n">
-        <v>6787807</v>
+        <v>6787844</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7253,10 +7261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121972920</v>
+        <v>121972885</v>
       </c>
       <c r="B61" t="n">
-        <v>92065</v>
+        <v>90801</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7265,25 +7273,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7293,10 +7301,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480994</v>
+        <v>481124</v>
       </c>
       <c r="R61" t="n">
-        <v>6787675</v>
+        <v>6787703</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7355,10 +7363,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121972889</v>
+        <v>121972916</v>
       </c>
       <c r="B62" t="n">
-        <v>92093</v>
+        <v>92077</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7367,25 +7375,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7395,10 +7403,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481131</v>
+        <v>480915</v>
       </c>
       <c r="R62" t="n">
-        <v>6787677</v>
+        <v>6787807</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7457,10 +7465,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121972918</v>
+        <v>121972913</v>
       </c>
       <c r="B63" t="n">
-        <v>92065</v>
+        <v>78388</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7469,25 +7477,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7497,10 +7505,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480812</v>
+        <v>480935</v>
       </c>
       <c r="R63" t="n">
-        <v>6787702</v>
+        <v>6787807</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7559,10 +7567,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121972911</v>
+        <v>121972918</v>
       </c>
       <c r="B64" t="n">
-        <v>92057</v>
+        <v>92077</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7571,38 +7579,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480843</v>
+        <v>480812</v>
       </c>
       <c r="R64" t="n">
-        <v>6787540</v>
+        <v>6787702</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7661,10 +7669,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121972884</v>
+        <v>121972911</v>
       </c>
       <c r="B65" t="n">
-        <v>86314</v>
+        <v>92069</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7677,37 +7685,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3690</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480986</v>
+        <v>480843</v>
       </c>
       <c r="R65" t="n">
-        <v>6787836</v>
+        <v>6787540</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7740,11 +7745,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7771,10 +7771,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121972907</v>
+        <v>121972898</v>
       </c>
       <c r="B66" t="n">
-        <v>92077</v>
+        <v>92093</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7783,25 +7783,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480936</v>
+        <v>480829</v>
       </c>
       <c r="R66" t="n">
-        <v>6787692</v>
+        <v>6787731</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7873,10 +7873,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121972890</v>
+        <v>121972912</v>
       </c>
       <c r="B67" t="n">
-        <v>92093</v>
+        <v>92274</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7889,34 +7889,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480809</v>
+        <v>480966</v>
       </c>
       <c r="R67" t="n">
-        <v>6787568</v>
+        <v>6787791</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
         <v>121972883</v>
       </c>
       <c r="B68" t="n">
-        <v>78680</v>
+        <v>78685</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8077,10 +8077,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121972897</v>
+        <v>121972890</v>
       </c>
       <c r="B69" t="n">
-        <v>92081</v>
+        <v>92105</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8093,34 +8093,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481022</v>
+        <v>480809</v>
       </c>
       <c r="R69" t="n">
-        <v>6787739</v>
+        <v>6787568</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8179,10 +8179,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121972892</v>
+        <v>121972917</v>
       </c>
       <c r="B70" t="n">
-        <v>92093</v>
+        <v>92077</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8191,38 +8191,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480843</v>
+        <v>480797</v>
       </c>
       <c r="R70" t="n">
-        <v>6787540</v>
+        <v>6787722</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8281,10 +8281,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121972921</v>
+        <v>121972901</v>
       </c>
       <c r="B71" t="n">
-        <v>92065</v>
+        <v>92093</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8293,25 +8293,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480761</v>
+        <v>480745</v>
       </c>
       <c r="R71" t="n">
-        <v>6787650</v>
+        <v>6787692</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121972912</v>
+        <v>121972907</v>
       </c>
       <c r="B72" t="n">
-        <v>92262</v>
+        <v>92089</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,25 +8395,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2079</v>
+        <v>4366</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480966</v>
+        <v>480936</v>
       </c>
       <c r="R72" t="n">
-        <v>6787791</v>
+        <v>6787692</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1490,7 +1490,7 @@
         <v>112924074</v>
       </c>
       <c r="B9" t="n">
-        <v>56756</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,11 +1529,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ekentjärnarna (Ekentjärnarna), Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481018</v>
+        <v>481017</v>
       </c>
       <c r="R9" t="n">
         <v>6787651</v>
@@ -4204,7 +4204,7 @@
         <v>112980896</v>
       </c>
       <c r="B33" t="n">
-        <v>56765</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4243,11 +4243,11 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480918</v>
+        <v>480919</v>
       </c>
       <c r="R33" t="n">
         <v>6787525</v>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -4312,7 +4312,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -4312,7 +4312,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1490,7 +1490,7 @@
         <v>112924074</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>112980896</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95895917</v>
+        <v>112922205</v>
       </c>
       <c r="B2" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480826.0730271254</v>
+        <v>480810</v>
       </c>
       <c r="R2" t="n">
-        <v>6787548.306375882</v>
+        <v>6787588</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,34 +765,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112914136</v>
+        <v>112923603</v>
       </c>
       <c r="B3" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,40 +794,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480780</v>
+        <v>480882</v>
       </c>
       <c r="R3" t="n">
-        <v>6787640</v>
+        <v>6787809</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,34 +873,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112914094</v>
+        <v>112923839</v>
       </c>
       <c r="B4" t="n">
-        <v>89968</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,37 +902,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480743</v>
+        <v>481014</v>
       </c>
       <c r="R4" t="n">
-        <v>6787695</v>
+        <v>6787750</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,12 +957,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,34 +981,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112923198</v>
+        <v>112989647</v>
       </c>
       <c r="B5" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,38 +1010,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>SV, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480817</v>
+        <v>480805</v>
       </c>
       <c r="R5" t="n">
-        <v>6787577</v>
+        <v>6787746</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,27 +1067,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,72 +1086,70 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112924028</v>
+        <v>112989839</v>
       </c>
       <c r="B6" t="n">
-        <v>8428</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ekentjärnarna (Ekentjärnarna), Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481018</v>
+        <v>481003</v>
       </c>
       <c r="R6" t="n">
-        <v>6787651</v>
+        <v>6787803</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,22 +1173,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,78 +1192,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112923242</v>
+        <v>112989992</v>
       </c>
       <c r="B7" t="n">
-        <v>91210</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480760</v>
+        <v>481125</v>
       </c>
       <c r="R7" t="n">
-        <v>6787645</v>
+        <v>6787708</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1323,22 +1279,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,78 +1298,64 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112922930</v>
+        <v>121972883</v>
       </c>
       <c r="B8" t="n">
-        <v>91210</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480779</v>
+        <v>480860</v>
       </c>
       <c r="R8" t="n">
-        <v>6787677</v>
+        <v>6787521</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,22 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,27 +1402,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112924074</v>
+        <v>112996024</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,43 +1425,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481017</v>
+        <v>480875</v>
       </c>
       <c r="R9" t="n">
-        <v>6787651</v>
+        <v>6787485</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,22 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,66 +1499,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112922923</v>
+        <v>119565457</v>
       </c>
       <c r="B10" t="n">
-        <v>91210</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480772</v>
+        <v>480985</v>
       </c>
       <c r="R10" t="n">
-        <v>6787679</v>
+        <v>6787569</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,22 +1578,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,33 +1602,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112924155</v>
+        <v>121972885</v>
       </c>
       <c r="B11" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,38 +1632,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480927</v>
+        <v>481124</v>
       </c>
       <c r="R11" t="n">
-        <v>6787700</v>
+        <v>6787703</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1789,22 +1686,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,27 +1706,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112923898</v>
+        <v>95895917</v>
       </c>
       <c r="B12" t="n">
-        <v>91253</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,48 +1729,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5448</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480942</v>
+        <v>480826</v>
       </c>
       <c r="R12" t="n">
-        <v>6787720</v>
+        <v>6787548</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,22 +1790,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,27 +1811,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112923064</v>
+        <v>112996023</v>
       </c>
       <c r="B13" t="n">
-        <v>56901</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,47 +1834,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480817</v>
+        <v>480874</v>
       </c>
       <c r="R13" t="n">
-        <v>6787577</v>
+        <v>6787486</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2035,22 +1888,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,66 +1908,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112923603</v>
+        <v>119342591</v>
       </c>
       <c r="B14" t="n">
-        <v>78060</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>1439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Sammetstaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum martioflavum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Unnån, Ekentjärnarna, Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480882</v>
+        <v>480814</v>
       </c>
       <c r="R14" t="n">
-        <v>6787810</v>
+        <v>6787531</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2148,22 +1985,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,75 +2015,63 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112922790</v>
+        <v>119096505</v>
       </c>
       <c r="B15" t="n">
-        <v>91226</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480742</v>
+        <v>480846</v>
       </c>
       <c r="R15" t="n">
-        <v>6787677</v>
+        <v>6787516</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2270,22 +2095,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,72 +2119,82 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>I brant slänt på isälvssediment, mest gran i närheten, tall längre bort.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112922205</v>
+        <v>112922790</v>
       </c>
       <c r="B16" t="n">
-        <v>78060</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480809</v>
+        <v>480742</v>
       </c>
       <c r="R16" t="n">
-        <v>6787588</v>
+        <v>6787676</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2388,7 +2223,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,7 +2233,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,59 +2260,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112923140</v>
+        <v>121972895</v>
       </c>
       <c r="B17" t="n">
-        <v>8428</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480817</v>
+        <v>481073</v>
       </c>
       <c r="R17" t="n">
-        <v>6787577</v>
+        <v>6787790</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2501,22 +2325,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,63 +2345,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112923608</v>
+        <v>121972897</v>
       </c>
       <c r="B18" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480882</v>
+        <v>481022</v>
       </c>
       <c r="R18" t="n">
-        <v>6787810</v>
+        <v>6787739</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,22 +2422,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,66 +2442,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112924151</v>
+        <v>121972898</v>
       </c>
       <c r="B19" t="n">
-        <v>8428</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480927</v>
+        <v>480829</v>
       </c>
       <c r="R19" t="n">
-        <v>6787700</v>
+        <v>6787731</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2727,22 +2519,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,68 +2539,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112923512</v>
+        <v>121972901</v>
       </c>
       <c r="B20" t="n">
-        <v>8428</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480734</v>
+        <v>480745</v>
       </c>
       <c r="R20" t="n">
-        <v>6787669</v>
+        <v>6787692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,22 +2616,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2875,66 +2636,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112923839</v>
+        <v>112996034</v>
       </c>
       <c r="B21" t="n">
-        <v>78060</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481013</v>
+        <v>481123</v>
       </c>
       <c r="R21" t="n">
-        <v>6787750</v>
+        <v>6787706</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2958,22 +2713,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,77 +2733,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112981155</v>
+        <v>121972912</v>
       </c>
       <c r="B22" t="n">
-        <v>56786</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100110</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480930</v>
+        <v>480966</v>
       </c>
       <c r="R22" t="n">
-        <v>6787621</v>
+        <v>6787791</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3082,22 +2810,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3112,61 +2830,48 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112996030</v>
+        <v>121972884</v>
       </c>
       <c r="B23" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3175,13 +2880,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481005</v>
+        <v>480986</v>
       </c>
       <c r="R23" t="n">
-        <v>6787834</v>
+        <v>6787836</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3205,12 +2910,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,34 +2929,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112990060</v>
+        <v>119096496</v>
       </c>
       <c r="B24" t="n">
-        <v>90049</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,21 +2958,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3277,17 +2981,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481140</v>
+        <v>480846</v>
       </c>
       <c r="R24" t="n">
-        <v>6787582</v>
+        <v>6787516</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3311,17 +3015,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3337,27 +3036,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112996028</v>
+        <v>119565699</v>
       </c>
       <c r="B25" t="n">
-        <v>91313</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,37 +3059,48 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480995</v>
+        <v>480853</v>
       </c>
       <c r="R25" t="n">
-        <v>6787829</v>
+        <v>6787516</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3419,12 +3124,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,71 +3148,78 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112996032</v>
+        <v>119565742</v>
       </c>
       <c r="B26" t="n">
-        <v>89441</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5685</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Siljansleden, Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481080</v>
+        <v>480845</v>
       </c>
       <c r="R26" t="n">
-        <v>6787730</v>
+        <v>6787511</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3521,12 +3243,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3535,76 +3267,78 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112983978</v>
+        <v>119566308</v>
       </c>
       <c r="B27" t="n">
-        <v>5164</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ekentjärnarna (Ekentjärnarna), Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481104</v>
+        <v>480816</v>
       </c>
       <c r="R27" t="n">
-        <v>6787672</v>
+        <v>6787542</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,22 +3362,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3659,27 +3393,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112996033</v>
+        <v>119568829</v>
       </c>
       <c r="B28" t="n">
-        <v>77858</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,37 +3416,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481078</v>
+        <v>480735</v>
       </c>
       <c r="R28" t="n">
-        <v>6787734</v>
+        <v>6787658</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3741,12 +3477,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,33 +3491,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112996021</v>
+        <v>121972911</v>
       </c>
       <c r="B29" t="n">
-        <v>77858</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,34 +3521,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480899</v>
+        <v>480843</v>
       </c>
       <c r="R29" t="n">
-        <v>6787538</v>
+        <v>6787540</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3843,12 +3575,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3863,27 +3595,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112996022</v>
+        <v>112922923</v>
       </c>
       <c r="B30" t="n">
-        <v>78697</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3891,37 +3618,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480891</v>
+        <v>480772</v>
       </c>
       <c r="R30" t="n">
-        <v>6787558</v>
+        <v>6787679</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3945,12 +3673,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3965,27 +3703,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112989859</v>
+        <v>112922930</v>
       </c>
       <c r="B31" t="n">
-        <v>78140</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3993,40 +3726,47 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481003</v>
+        <v>480779</v>
       </c>
       <c r="R31" t="n">
-        <v>6787803</v>
+        <v>6787677</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4050,17 +3790,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4069,61 +3814,55 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112996031</v>
+        <v>112923242</v>
       </c>
       <c r="B32" t="n">
-        <v>91302</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4132,20 +3871,19 @@
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481064</v>
+        <v>480760</v>
       </c>
       <c r="R32" t="n">
-        <v>6787744</v>
+        <v>6787645</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4169,12 +3907,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4189,27 +3937,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112980896</v>
+        <v>112996027</v>
       </c>
       <c r="B33" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4217,40 +3960,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480919</v>
+        <v>480947</v>
       </c>
       <c r="R33" t="n">
-        <v>6787525</v>
+        <v>6787809</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4280,58 +4028,44 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:39</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:39</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112996027</v>
+        <v>112996030</v>
       </c>
       <c r="B34" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4354,7 +4088,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4370,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480947</v>
+        <v>481005</v>
       </c>
       <c r="R34" t="n">
-        <v>6787809</v>
+        <v>6787834</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4433,15 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112982228</v>
+        <v>112996037</v>
       </c>
       <c r="B35" t="n">
-        <v>56910</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4449,41 +4178,48 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Unnån (Unnån), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480787</v>
+        <v>481143</v>
       </c>
       <c r="R35" t="n">
-        <v>6787755</v>
+        <v>6787609</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4510,97 +4246,81 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112983991</v>
+        <v>119545661</v>
       </c>
       <c r="B36" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ekentjärnarna (Ekentjärnarna), Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481104</v>
+        <v>481008</v>
       </c>
       <c r="R36" t="n">
-        <v>6787672</v>
+        <v>6787840</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4624,22 +4344,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>rikligt, tiotals</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4660,22 +4375,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112996029</v>
+        <v>120837852</v>
       </c>
       <c r="B37" t="n">
-        <v>87584</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,27 +4393,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4714,13 +4428,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481008</v>
+        <v>481001</v>
       </c>
       <c r="R37" t="n">
-        <v>6787835</v>
+        <v>6787844</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4744,12 +4458,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4758,33 +4472,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112996036</v>
+        <v>121972915</v>
       </c>
       <c r="B38" t="n">
-        <v>78105</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,21 +4502,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4816,13 +4526,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481143</v>
+        <v>480914</v>
       </c>
       <c r="R38" t="n">
-        <v>6787599</v>
+        <v>6787844</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4846,12 +4556,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4866,27 +4576,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112989647</v>
+        <v>121972916</v>
       </c>
       <c r="B39" t="n">
-        <v>78140</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,40 +4599,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>SV, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480804</v>
+        <v>480915</v>
       </c>
       <c r="R39" t="n">
-        <v>6787746</v>
+        <v>6787807</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4951,17 +4653,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4970,38 +4667,32 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112996037</v>
+        <v>121972917</v>
       </c>
       <c r="B40" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5022,31 +4713,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481143</v>
+        <v>480797</v>
       </c>
       <c r="R40" t="n">
-        <v>6787610</v>
+        <v>6787722</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5070,12 +4750,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5084,38 +4764,32 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119545661</v>
+        <v>121972918</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5137,22 +4811,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481008</v>
+        <v>480812</v>
       </c>
       <c r="R41" t="n">
-        <v>6787840</v>
+        <v>6787702</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5176,17 +4847,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>rikligt, tiotals</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5195,34 +4861,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119568829</v>
+        <v>121972919</v>
       </c>
       <c r="B42" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5230,44 +4890,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480735</v>
+        <v>480773</v>
       </c>
       <c r="R42" t="n">
-        <v>6787658</v>
+        <v>6787678</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5291,12 +4944,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5305,34 +4958,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119566096</v>
+        <v>121972920</v>
       </c>
       <c r="B43" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5340,41 +4987,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480980</v>
+        <v>480994</v>
       </c>
       <c r="R43" t="n">
-        <v>6787594</v>
+        <v>6787675</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5398,22 +5041,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,27 +5061,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119568651</v>
+        <v>121972921</v>
       </c>
       <c r="B44" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5456,40 +5084,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481001</v>
+        <v>480761</v>
       </c>
       <c r="R44" t="n">
-        <v>6787625</v>
+        <v>6787650</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5513,17 +5138,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>flera</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5532,74 +5152,63 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120747281</v>
+        <v>121972922</v>
       </c>
       <c r="B45" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480845</v>
+        <v>480796</v>
       </c>
       <c r="R45" t="n">
-        <v>6787659</v>
+        <v>6787645</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5626,17 +5235,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5645,34 +5249,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120747198</v>
+        <v>127640071</v>
       </c>
       <c r="B46" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5680,37 +5278,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480878</v>
+        <v>480961</v>
       </c>
       <c r="R46" t="n">
-        <v>6787512</v>
+        <v>6787858</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5737,17 +5332,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5756,34 +5346,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120747228</v>
+        <v>112996031</v>
       </c>
       <c r="B47" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,40 +5375,48 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480890</v>
+        <v>481063</v>
       </c>
       <c r="R47" t="n">
-        <v>6787571</v>
+        <v>6787744</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5848,17 +5440,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5867,34 +5454,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120747170</v>
+        <v>121972907</v>
       </c>
       <c r="B48" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,37 +5483,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480886</v>
+        <v>480936</v>
       </c>
       <c r="R48" t="n">
-        <v>6787539</v>
+        <v>6787692</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5959,17 +5537,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5978,72 +5551,63 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120747402</v>
+        <v>112996025</v>
       </c>
       <c r="B49" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480831</v>
+        <v>480874</v>
       </c>
       <c r="R49" t="n">
-        <v>6787737</v>
+        <v>6787479</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6070,17 +5634,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6089,77 +5648,73 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120747340</v>
+        <v>112996029</v>
       </c>
       <c r="B50" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>4962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480847</v>
+        <v>481007</v>
       </c>
       <c r="R50" t="n">
-        <v>6787707</v>
+        <v>6787835</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6183,17 +5738,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6202,83 +5752,69 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120837852</v>
+        <v>112914094</v>
       </c>
       <c r="B51" t="n">
-        <v>91973</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481001</v>
+        <v>480743</v>
       </c>
       <c r="R51" t="n">
-        <v>6787844</v>
+        <v>6787694</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6302,12 +5838,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6323,65 +5859,63 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121972921</v>
+        <v>112990060</v>
       </c>
       <c r="B52" t="n">
-        <v>92077</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480761</v>
+        <v>481141</v>
       </c>
       <c r="R52" t="n">
-        <v>6787650</v>
+        <v>6787582</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6405,12 +5939,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6419,33 +5958,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121972884</v>
+        <v>112923898</v>
       </c>
       <c r="B53" t="n">
-        <v>86321</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6453,40 +5988,48 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3690</v>
+        <v>5448</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Soop</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480986</v>
+        <v>480942</v>
       </c>
       <c r="R53" t="n">
-        <v>6787836</v>
+        <v>6787720</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6510,17 +6053,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6529,55 +6077,51 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121972897</v>
+        <v>112996032</v>
       </c>
       <c r="B54" t="n">
-        <v>92093</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>5685</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6587,13 +6131,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481022</v>
+        <v>481080</v>
       </c>
       <c r="R54" t="n">
-        <v>6787739</v>
+        <v>6787730</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6617,12 +6161,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6637,27 +6181,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121972892</v>
+        <v>112996028</v>
       </c>
       <c r="B55" t="n">
-        <v>92105</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6665,37 +6204,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480843</v>
+        <v>480995</v>
       </c>
       <c r="R55" t="n">
-        <v>6787540</v>
+        <v>6787829</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6719,12 +6258,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6739,65 +6278,63 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121972922</v>
+        <v>96117407</v>
       </c>
       <c r="B56" t="n">
-        <v>92077</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480796</v>
+        <v>480781</v>
       </c>
       <c r="R56" t="n">
-        <v>6787645</v>
+        <v>6787572</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6821,12 +6358,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6835,71 +6372,85 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121972920</v>
+        <v>112914136</v>
       </c>
       <c r="B57" t="n">
-        <v>92077</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480994</v>
+        <v>480780</v>
       </c>
       <c r="R57" t="n">
-        <v>6787675</v>
+        <v>6787640</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6923,12 +6474,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6937,71 +6493,68 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121972889</v>
+        <v>112923198</v>
       </c>
       <c r="B58" t="n">
-        <v>92105</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481131</v>
+        <v>480817</v>
       </c>
       <c r="R58" t="n">
-        <v>6787677</v>
+        <v>6787576</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7025,12 +6578,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7045,62 +6613,58 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121972919</v>
+        <v>112923608</v>
       </c>
       <c r="B59" t="n">
-        <v>92077</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480773</v>
+        <v>480882</v>
       </c>
       <c r="R59" t="n">
-        <v>6787678</v>
+        <v>6787809</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7127,12 +6691,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7147,65 +6721,61 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121972915</v>
+        <v>112924155</v>
       </c>
       <c r="B60" t="n">
-        <v>92077</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480914</v>
+        <v>480927</v>
       </c>
       <c r="R60" t="n">
-        <v>6787844</v>
+        <v>6787699</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7229,12 +6799,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7249,49 +6829,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121972885</v>
+        <v>112996036</v>
       </c>
       <c r="B61" t="n">
-        <v>90801</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7301,13 +6876,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481124</v>
+        <v>481143</v>
       </c>
       <c r="R61" t="n">
-        <v>6787703</v>
+        <v>6787598</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7331,12 +6906,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7351,62 +6926,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121972916</v>
+        <v>120747170</v>
       </c>
       <c r="B62" t="n">
-        <v>92077</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480915</v>
+        <v>480886</v>
       </c>
       <c r="R62" t="n">
-        <v>6787807</v>
+        <v>6787539</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7433,12 +7006,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7447,68 +7025,67 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121972913</v>
+        <v>120747198</v>
       </c>
       <c r="B63" t="n">
-        <v>78388</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480935</v>
+        <v>480878</v>
       </c>
       <c r="R63" t="n">
-        <v>6787807</v>
+        <v>6787512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7535,12 +7112,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7549,68 +7131,67 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121972918</v>
+        <v>120747228</v>
       </c>
       <c r="B64" t="n">
-        <v>92077</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480812</v>
+        <v>480890</v>
       </c>
       <c r="R64" t="n">
-        <v>6787702</v>
+        <v>6787571</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7637,12 +7218,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7651,68 +7237,67 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121972911</v>
+        <v>120747402</v>
       </c>
       <c r="B65" t="n">
-        <v>92069</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480843</v>
+        <v>480831</v>
       </c>
       <c r="R65" t="n">
-        <v>6787540</v>
+        <v>6787737</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7739,12 +7324,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7753,33 +7343,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121972898</v>
+        <v>112996022</v>
       </c>
       <c r="B66" t="n">
-        <v>92093</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7787,21 +7373,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7811,13 +7397,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480829</v>
+        <v>480891</v>
       </c>
       <c r="R66" t="n">
-        <v>6787731</v>
+        <v>6787557</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7841,12 +7427,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7861,27 +7447,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121972912</v>
+        <v>112924074</v>
       </c>
       <c r="B67" t="n">
-        <v>92274</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7889,37 +7470,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480966</v>
+        <v>481017</v>
       </c>
       <c r="R67" t="n">
-        <v>6787791</v>
+        <v>6787651</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7943,12 +7530,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7963,27 +7560,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121972883</v>
+        <v>112980896</v>
       </c>
       <c r="B68" t="n">
-        <v>78685</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7991,37 +7583,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480860</v>
+        <v>480919</v>
       </c>
       <c r="R68" t="n">
-        <v>6787521</v>
+        <v>6787525</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8045,12 +7643,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8065,27 +7673,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121972890</v>
+        <v>112983277</v>
       </c>
       <c r="B69" t="n">
-        <v>92105</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8093,37 +7696,45 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480809</v>
+        <v>481142</v>
       </c>
       <c r="R69" t="n">
-        <v>6787568</v>
+        <v>6787700</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8147,12 +7758,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8167,65 +7788,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121972917</v>
+        <v>125106308</v>
       </c>
       <c r="B70" t="n">
-        <v>92077</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480797</v>
+        <v>480781</v>
       </c>
       <c r="R70" t="n">
-        <v>6787722</v>
+        <v>6787572</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8249,12 +7865,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Hackmärken färska i gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8269,62 +7900,62 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121972901</v>
+        <v>112983978</v>
       </c>
       <c r="B71" t="n">
-        <v>92093</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2059</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480745</v>
+        <v>481104</v>
       </c>
       <c r="R71" t="n">
-        <v>6787692</v>
+        <v>6787672</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8351,12 +7982,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8365,33 +8006,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121972907</v>
+        <v>112996035</v>
       </c>
       <c r="B72" t="n">
-        <v>92089</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8399,37 +8036,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4366</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480936</v>
+        <v>481128</v>
       </c>
       <c r="R72" t="n">
-        <v>6787692</v>
+        <v>6787712</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8453,12 +8099,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8467,21 +8113,2146 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>121972923</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>481148</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6787700</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
           <t>Maria Hindemo</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
+      <c r="AX73" t="inlineStr">
         <is>
           <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>112923064</v>
+      </c>
+      <c r="B74" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Unnån, Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>480817</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6787576</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>112982228</v>
+      </c>
+      <c r="B75" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Unnån, Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>480787</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6787755</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>121972882</v>
+      </c>
+      <c r="B76" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>481148</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6787700</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>112923140</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Unnån, Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>480817</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6787576</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>112923512</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Unnån, Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>480733</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6787668</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>112924028</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>481017</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6787651</v>
+      </c>
+      <c r="S79" t="n">
+        <v>20</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>112924151</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Unnån, Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>480927</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6787699</v>
+      </c>
+      <c r="S80" t="n">
+        <v>50</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>112983991</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>481104</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6787672</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120747281</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Ekentjärnskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>480845</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6787659</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120747340</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Ekentjärnskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>480847</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6787707</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>119568643</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>481007</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6787620</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125187193</v>
+      </c>
+      <c r="B85" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>480717</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6787597</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>112996021</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>480899</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6787538</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>112996033</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>481079</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6787734</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121972913</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>480935</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6787807</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>119568677</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>480971</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6787547</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120747144</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Ekentjärnskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>480904</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6787507</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120747368</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Ekentjärnskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>480840</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6787710</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>på tall</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125105944</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>V Ekentjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>481003</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6787803</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AZ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112922205</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923603</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923839</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112989647</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112989839</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972883</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119565457</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95895917</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996023</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119342591</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119096505</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2054,6 +2119,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112922790</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2151,6 +2221,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972897</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2248,6 +2323,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972898</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2345,6 +2425,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972901</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2442,6 +2527,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972912</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2547,6 +2637,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972884</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2648,6 +2743,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119096496</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2767,6 +2867,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119565699</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2886,6 +2991,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119565742</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3005,6 +3115,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119566308</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3110,6 +3225,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119568829</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3207,6 +3327,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972911</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3315,6 +3440,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112922923</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3432,6 +3562,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112922930</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3549,6 +3684,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923242</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3658,6 +3798,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996027</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3767,6 +3912,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996030</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3873,6 +4023,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119545661</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3982,6 +4137,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120837852</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4079,6 +4239,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972915</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4176,6 +4341,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972916</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4273,6 +4443,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972917</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4370,6 +4545,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972918</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4467,6 +4647,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972919</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4564,6 +4749,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972920</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4661,6 +4851,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972921</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4758,6 +4953,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972922</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4855,6 +5055,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127640071</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4952,6 +5157,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972907</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5049,6 +5259,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5153,6 +5368,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996029</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5254,6 +5474,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112914094</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5373,6 +5598,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923898</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5470,6 +5700,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996028</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5586,6 +5821,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96117407</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5692,6 +5932,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112914136</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5805,6 +6050,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923198</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5913,6 +6163,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923608</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6021,6 +6276,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112924155</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6127,6 +6387,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120747170</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6233,6 +6498,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120747198</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6339,6 +6609,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120747228</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6445,6 +6720,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120747402</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6542,6 +6822,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996022</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6655,6 +6940,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112924074</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6768,6 +7058,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112980896</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6880,6 +7175,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125106308</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6997,6 +7297,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923064</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7108,6 +7413,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982228</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7221,6 +7531,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923140</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7334,6 +7649,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923512</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7442,6 +7762,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112924028</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7550,6 +7875,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112924151</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7658,6 +7988,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120747281</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7766,6 +8101,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120747340</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7876,6 +8216,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119568643</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7982,6 +8327,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125187193</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8079,6 +8429,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996021</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8176,6 +8531,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972913</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8281,6 +8641,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119568677</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8387,6 +8752,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120747144</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8493,6 +8863,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120747368</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8600,6 +8975,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125105944</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8706,6 +9086,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112989992</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8803,6 +9188,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972885</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8900,6 +9290,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972895</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8997,6 +9392,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996034</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9106,6 +9506,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996037</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9214,6 +9619,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996031</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9320,6 +9730,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112990060</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9417,6 +9832,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996032</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9514,6 +9934,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996036</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9629,6 +10054,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983277</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9742,6 +10172,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983978</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9849,6 +10284,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996035</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9946,6 +10386,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972923</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10043,6 +10488,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972882</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10156,6 +10606,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983991</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10253,8 +10708,106 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996033</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ92"/>
+  <dimension ref="A1:AZ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112996024</v>
+        <v>135721948</v>
       </c>
       <c r="B8" t="n">
-        <v>92208</v>
+        <v>79470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,37 +1354,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480875</v>
+        <v>480816</v>
       </c>
       <c r="R8" t="n">
-        <v>6787485</v>
+        <v>6787643</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,12 +1408,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka ex på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,31 +1439,46 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996024</t>
+          <t>https://artportalen.se/Sighting/135721948</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119565457</v>
+        <v>112996024</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,39 +1486,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480985</v>
+        <v>480875</v>
       </c>
       <c r="R9" t="n">
-        <v>6787569</v>
+        <v>6787485</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,22 +1540,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,34 +1554,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565457</t>
+          <t>https://artportalen.se/Sighting/112996024</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95895917</v>
+        <v>119565457</v>
       </c>
       <c r="B10" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,44 +1588,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480826</v>
+        <v>480985</v>
       </c>
       <c r="R10" t="n">
-        <v>6787548</v>
+        <v>6787569</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,12 +1644,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,24 +1675,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95895917</t>
+          <t>https://artportalen.se/Sighting/119565457</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112996023</v>
+        <v>95895917</v>
       </c>
       <c r="B11" t="n">
         <v>92369</v>
@@ -1698,17 +1720,24 @@
           <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480874</v>
+        <v>480826</v>
       </c>
       <c r="R11" t="n">
-        <v>6787486</v>
+        <v>6787548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,12 +1764,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,71 +1778,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996023</t>
+          <t>https://artportalen.se/Sighting/95895917</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119342591</v>
+        <v>112996023</v>
       </c>
       <c r="B12" t="n">
-        <v>93206</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1439</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sammetstaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum martioflavum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480814</v>
+        <v>480874</v>
       </c>
       <c r="R12" t="n">
-        <v>6787531</v>
+        <v>6787486</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,22 +1867,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,68 +1887,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119342591</t>
+          <t>https://artportalen.se/Sighting/112996023</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119096505</v>
+        <v>119342591</v>
       </c>
       <c r="B13" t="n">
-        <v>91394</v>
+        <v>93206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2051</v>
+        <v>1439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Sammetstaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum martioflavum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480846</v>
+        <v>480814</v>
       </c>
       <c r="R13" t="n">
-        <v>6787516</v>
+        <v>6787531</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1957,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1976,14 +1993,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>I brant slänt på isälvssediment, mest gran i närheten, tall längre bort.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1993,22 +2004,22 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119096505</t>
+          <t>https://artportalen.se/Sighting/119342591</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112922790</v>
+        <v>119096505</v>
       </c>
       <c r="B14" t="n">
-        <v>93213</v>
+        <v>91394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,47 +2027,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480742</v>
+        <v>480846</v>
       </c>
       <c r="R14" t="n">
-        <v>6787676</v>
+        <v>6787516</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2080,22 +2084,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,30 +2108,36 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>I brant slänt på isälvssediment, mest gran i närheten, tall längre bort.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922790</t>
+          <t>https://artportalen.se/Sighting/119096505</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121972897</v>
+        <v>112922790</v>
       </c>
       <c r="B15" t="n">
         <v>93213</v>
@@ -2155,20 +2165,30 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481022</v>
+        <v>480742</v>
       </c>
       <c r="R15" t="n">
-        <v>6787739</v>
+        <v>6787676</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,12 +2212,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,24 +2242,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972897</t>
+          <t>https://artportalen.se/Sighting/112922790</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121972898</v>
+        <v>121972897</v>
       </c>
       <c r="B16" t="n">
         <v>93213</v>
@@ -2264,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480829</v>
+        <v>481022</v>
       </c>
       <c r="R16" t="n">
-        <v>6787731</v>
+        <v>6787739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,13 +2355,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972898</t>
+          <t>https://artportalen.se/Sighting/121972897</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121972901</v>
+        <v>121972898</v>
       </c>
       <c r="B17" t="n">
         <v>93213</v>
@@ -2366,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480745</v>
+        <v>480829</v>
       </c>
       <c r="R17" t="n">
-        <v>6787692</v>
+        <v>6787731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,38 +2457,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972901</t>
+          <t>https://artportalen.se/Sighting/121972898</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121972912</v>
+        <v>121972901</v>
       </c>
       <c r="B18" t="n">
-        <v>91962</v>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480966</v>
+        <v>480745</v>
       </c>
       <c r="R18" t="n">
-        <v>6787791</v>
+        <v>6787692</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,16 +2559,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972912</t>
+          <t>https://artportalen.se/Sighting/121972901</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121972884</v>
+        <v>121972912</v>
       </c>
       <c r="B19" t="n">
-        <v>87325</v>
+        <v>91962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,37 +2576,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3690</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480986</v>
+        <v>480966</v>
       </c>
       <c r="R19" t="n">
-        <v>6787836</v>
+        <v>6787791</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,11 +2638,6 @@
           <t>2024-09-03</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2639,16 +2661,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972884</t>
+          <t>https://artportalen.se/Sighting/121972912</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119096496</v>
+        <v>121972884</v>
       </c>
       <c r="B20" t="n">
-        <v>93189</v>
+        <v>87325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,17 +2701,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480846</v>
+        <v>480986</v>
       </c>
       <c r="R20" t="n">
-        <v>6787516</v>
+        <v>6787836</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2713,12 +2735,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2727,7 +2754,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2745,13 +2771,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119096496</t>
+          <t>https://artportalen.se/Sighting/121972884</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119565699</v>
+        <v>119096496</v>
       </c>
       <c r="B21" t="n">
         <v>93189</v>
@@ -2779,31 +2805,23 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480853</v>
+        <v>480846</v>
       </c>
       <c r="R21" t="n">
         <v>6787516</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2827,22 +2845,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,24 +2866,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565699</t>
+          <t>https://artportalen.se/Sighting/119096496</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119565742</v>
+        <v>119565699</v>
       </c>
       <c r="B22" t="n">
         <v>93189</v>
@@ -2905,7 +2913,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2917,14 +2925,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Siljansleden, Siljansleden, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480845</v>
+        <v>480853</v>
       </c>
       <c r="R22" t="n">
-        <v>6787511</v>
+        <v>6787516</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2956,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2966,7 +2974,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,13 +3001,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565742</t>
+          <t>https://artportalen.se/Sighting/119565699</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119566308</v>
+        <v>119565742</v>
       </c>
       <c r="B23" t="n">
         <v>93189</v>
@@ -3029,7 +3037,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3041,14 +3049,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Siljansleden, Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480816</v>
+        <v>480845</v>
       </c>
       <c r="R23" t="n">
-        <v>6787542</v>
+        <v>6787511</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3080,7 +3088,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3090,7 +3098,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3117,13 +3125,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119566308</t>
+          <t>https://artportalen.se/Sighting/119565742</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119568829</v>
+        <v>119566308</v>
       </c>
       <c r="B24" t="n">
         <v>93189</v>
@@ -3153,25 +3161,29 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480735</v>
+        <v>480816</v>
       </c>
       <c r="R24" t="n">
-        <v>6787658</v>
+        <v>6787542</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3198,9 +3210,19 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3216,24 +3238,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568829</t>
+          <t>https://artportalen.se/Sighting/119566308</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121972911</v>
+        <v>119568829</v>
       </c>
       <c r="B25" t="n">
         <v>93189</v>
@@ -3261,20 +3283,27 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480843</v>
+        <v>480735</v>
       </c>
       <c r="R25" t="n">
-        <v>6787540</v>
+        <v>6787658</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,12 +3327,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,33 +3341,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972911</t>
+          <t>https://artportalen.se/Sighting/119568829</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112922923</v>
+        <v>121972911</v>
       </c>
       <c r="B26" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3346,38 +3376,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480772</v>
+        <v>480843</v>
       </c>
       <c r="R26" t="n">
-        <v>6787679</v>
+        <v>6787540</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3401,22 +3430,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,24 +3450,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922923</t>
+          <t>https://artportalen.se/Sighting/121972911</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112922930</v>
+        <v>112922923</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3476,16 +3495,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3493,13 +3503,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480779</v>
+        <v>480772</v>
       </c>
       <c r="R27" t="n">
-        <v>6787677</v>
+        <v>6787679</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3528,7 +3538,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3538,7 +3548,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,13 +3574,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922930</t>
+          <t>https://artportalen.se/Sighting/112922923</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112923242</v>
+        <v>112922930</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3600,7 +3610,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3615,13 +3625,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480760</v>
+        <v>480779</v>
       </c>
       <c r="R28" t="n">
-        <v>6787645</v>
+        <v>6787677</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3650,7 +3660,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3660,7 +3670,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3686,13 +3696,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923242</t>
+          <t>https://artportalen.se/Sighting/112922930</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112996027</v>
+        <v>112923242</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3722,7 +3732,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3731,17 +3741,16 @@
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480947</v>
+        <v>480760</v>
       </c>
       <c r="R29" t="n">
-        <v>6787809</v>
+        <v>6787645</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3768,12 +3777,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3782,31 +3801,30 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996027</t>
+          <t>https://artportalen.se/Sighting/112923242</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112996030</v>
+        <v>112996027</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3836,7 +3854,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3852,10 +3870,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481005</v>
+        <v>480947</v>
       </c>
       <c r="R30" t="n">
-        <v>6787834</v>
+        <v>6787809</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3914,13 +3932,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996030</t>
+          <t>https://artportalen.se/Sighting/112996027</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119545661</v>
+        <v>112996030</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3948,8 +3966,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3958,13 +3984,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481008</v>
+        <v>481005</v>
       </c>
       <c r="R31" t="n">
-        <v>6787840</v>
+        <v>6787834</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3988,17 +4014,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>rikligt, tiotals</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,24 +4035,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119545661</t>
+          <t>https://artportalen.se/Sighting/112996030</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120837852</v>
+        <v>119545661</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -4059,16 +4080,8 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4077,13 +4090,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481001</v>
+        <v>481008</v>
       </c>
       <c r="R32" t="n">
-        <v>6787844</v>
+        <v>6787840</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4107,12 +4120,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>rikligt, tiotals</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,24 +4146,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120837852</t>
+          <t>https://artportalen.se/Sighting/119545661</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121972915</v>
+        <v>120837852</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4173,14 +4191,25 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480914</v>
+        <v>481001</v>
       </c>
       <c r="R33" t="n">
         <v>6787844</v>
@@ -4210,12 +4239,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,30 +4253,31 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972915</t>
+          <t>https://artportalen.se/Sighting/120837852</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121972916</v>
+        <v>121972915</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4282,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480915</v>
+        <v>480914</v>
       </c>
       <c r="R34" t="n">
-        <v>6787807</v>
+        <v>6787844</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,13 +4373,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972916</t>
+          <t>https://artportalen.se/Sighting/121972915</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121972917</v>
+        <v>121972916</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4384,10 +4414,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480797</v>
+        <v>480915</v>
       </c>
       <c r="R35" t="n">
-        <v>6787722</v>
+        <v>6787807</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4445,13 +4475,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972917</t>
+          <t>https://artportalen.se/Sighting/121972916</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121972918</v>
+        <v>121972917</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4486,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480812</v>
+        <v>480797</v>
       </c>
       <c r="R36" t="n">
-        <v>6787702</v>
+        <v>6787722</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4547,13 +4577,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972918</t>
+          <t>https://artportalen.se/Sighting/121972917</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121972919</v>
+        <v>121972918</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4588,10 +4618,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480773</v>
+        <v>480812</v>
       </c>
       <c r="R37" t="n">
-        <v>6787678</v>
+        <v>6787702</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4649,13 +4679,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972919</t>
+          <t>https://artportalen.se/Sighting/121972918</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121972920</v>
+        <v>121972919</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4690,10 +4720,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480994</v>
+        <v>480773</v>
       </c>
       <c r="R38" t="n">
-        <v>6787675</v>
+        <v>6787678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4751,13 +4781,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972920</t>
+          <t>https://artportalen.se/Sighting/121972919</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121972921</v>
+        <v>121972920</v>
       </c>
       <c r="B39" t="n">
         <v>93197</v>
@@ -4792,10 +4822,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480761</v>
+        <v>480994</v>
       </c>
       <c r="R39" t="n">
-        <v>6787650</v>
+        <v>6787675</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4853,13 +4883,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972921</t>
+          <t>https://artportalen.se/Sighting/121972920</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121972922</v>
+        <v>121972921</v>
       </c>
       <c r="B40" t="n">
         <v>93197</v>
@@ -4894,10 +4924,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480796</v>
+        <v>480761</v>
       </c>
       <c r="R40" t="n">
-        <v>6787645</v>
+        <v>6787650</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4955,13 +4985,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972922</t>
+          <t>https://artportalen.se/Sighting/121972921</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127640071</v>
+        <v>121972922</v>
       </c>
       <c r="B41" t="n">
         <v>93197</v>
@@ -4992,14 +5022,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480961</v>
+        <v>480796</v>
       </c>
       <c r="R41" t="n">
-        <v>6787858</v>
+        <v>6787645</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5026,12 +5056,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5046,27 +5076,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127640071</t>
+          <t>https://artportalen.se/Sighting/121972922</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121972907</v>
+        <v>127640071</v>
       </c>
       <c r="B42" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5074,34 +5104,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480936</v>
+        <v>480961</v>
       </c>
       <c r="R42" t="n">
-        <v>6787692</v>
+        <v>6787858</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5128,12 +5158,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5148,49 +5178,49 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972907</t>
+          <t>https://artportalen.se/Sighting/127640071</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112996025</v>
+        <v>121972907</v>
       </c>
       <c r="B43" t="n">
-        <v>91893</v>
+        <v>93209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4660</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5200,10 +5230,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480874</v>
+        <v>480936</v>
       </c>
       <c r="R43" t="n">
-        <v>6787479</v>
+        <v>6787692</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5230,12 +5260,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5250,72 +5280,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996025</t>
+          <t>https://artportalen.se/Sighting/121972907</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112996029</v>
+        <v>112996025</v>
       </c>
       <c r="B44" t="n">
-        <v>90522</v>
+        <v>91893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4962</v>
+        <v>4660</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481007</v>
+        <v>480874</v>
       </c>
       <c r="R44" t="n">
-        <v>6787835</v>
+        <v>6787479</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5370,16 +5393,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996029</t>
+          <t>https://artportalen.se/Sighting/112996025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112914094</v>
+        <v>112996029</v>
       </c>
       <c r="B45" t="n">
-        <v>91930</v>
+        <v>90522</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5387,37 +5410,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>4962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480743</v>
+        <v>481007</v>
       </c>
       <c r="R45" t="n">
-        <v>6787694</v>
+        <v>6787835</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5444,12 +5471,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5458,34 +5485,33 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914094</t>
+          <t>https://artportalen.se/Sighting/112996029</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112923898</v>
+        <v>112914094</v>
       </c>
       <c r="B46" t="n">
-        <v>93223</v>
+        <v>91930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5493,45 +5519,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480942</v>
+        <v>480743</v>
       </c>
       <c r="R46" t="n">
-        <v>6787720</v>
+        <v>6787694</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,22 +5576,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5589,27 +5597,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923898</t>
+          <t>https://artportalen.se/Sighting/112914094</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112996028</v>
+        <v>112923898</v>
       </c>
       <c r="B47" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5617,37 +5625,48 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480995</v>
+        <v>480942</v>
       </c>
       <c r="R47" t="n">
-        <v>6787829</v>
+        <v>6787720</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5671,12 +5690,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5685,71 +5714,69 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996028</t>
+          <t>https://artportalen.se/Sighting/112923898</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96117407</v>
+        <v>112996028</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480781</v>
+        <v>480995</v>
       </c>
       <c r="R48" t="n">
-        <v>6787572</v>
+        <v>6787829</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5776,12 +5803,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5790,46 +5817,30 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117407</t>
+          <t>https://artportalen.se/Sighting/112996028</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112914136</v>
+        <v>96117407</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5863,14 +5874,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480780</v>
+        <v>480781</v>
       </c>
       <c r="R49" t="n">
-        <v>6787640</v>
+        <v>6787572</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5897,17 +5908,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5920,6 +5926,21 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
@@ -5934,13 +5955,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914136</t>
+          <t>https://artportalen.se/Sighting/96117407</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112923198</v>
+        <v>112914136</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5969,20 +5990,22 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480817</v>
+        <v>480780</v>
       </c>
       <c r="R50" t="n">
-        <v>6787576</v>
+        <v>6787640</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6006,27 +6029,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6035,30 +6048,31 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923198</t>
+          <t>https://artportalen.se/Sighting/112914136</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112923608</v>
+        <v>112923198</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6094,13 +6108,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480882</v>
+        <v>480817</v>
       </c>
       <c r="R51" t="n">
-        <v>6787809</v>
+        <v>6787576</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6129,7 +6143,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6139,7 +6153,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6165,13 +6184,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923608</t>
+          <t>https://artportalen.se/Sighting/112923198</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112924155</v>
+        <v>112923608</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6207,13 +6226,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480927</v>
+        <v>480882</v>
       </c>
       <c r="R52" t="n">
-        <v>6787699</v>
+        <v>6787809</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6242,7 +6261,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6252,7 +6271,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6278,13 +6297,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924155</t>
+          <t>https://artportalen.se/Sighting/112923608</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120747170</v>
+        <v>112924155</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6313,22 +6332,20 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480886</v>
+        <v>480927</v>
       </c>
       <c r="R53" t="n">
-        <v>6787539</v>
+        <v>6787699</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6352,17 +6369,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6371,31 +6393,30 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747170</t>
+          <t>https://artportalen.se/Sighting/112924155</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120747198</v>
+        <v>120747170</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6433,10 +6454,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480878</v>
+        <v>480886</v>
       </c>
       <c r="R54" t="n">
-        <v>6787512</v>
+        <v>6787539</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6500,13 +6521,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747198</t>
+          <t>https://artportalen.se/Sighting/120747170</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120747228</v>
+        <v>120747198</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6544,10 +6565,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480890</v>
+        <v>480878</v>
       </c>
       <c r="R55" t="n">
-        <v>6787571</v>
+        <v>6787512</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6611,13 +6632,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747228</t>
+          <t>https://artportalen.se/Sighting/120747198</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120747402</v>
+        <v>120747228</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6655,10 +6676,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480831</v>
+        <v>480890</v>
       </c>
       <c r="R56" t="n">
-        <v>6787737</v>
+        <v>6787571</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6722,54 +6743,57 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747402</t>
+          <t>https://artportalen.se/Sighting/120747228</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112996022</v>
+        <v>120747402</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480891</v>
+        <v>480831</v>
       </c>
       <c r="R57" t="n">
-        <v>6787557</v>
+        <v>6787737</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6793,12 +6817,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6807,33 +6836,34 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996022</t>
+          <t>https://artportalen.se/Sighting/120747402</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112924074</v>
+        <v>112996022</v>
       </c>
       <c r="B58" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6841,43 +6871,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481017</v>
+        <v>480891</v>
       </c>
       <c r="R58" t="n">
-        <v>6787651</v>
+        <v>6787557</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6901,22 +6925,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6931,24 +6945,24 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924074</t>
+          <t>https://artportalen.se/Sighting/112996022</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112980896</v>
+        <v>112924074</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -6985,17 +6999,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480919</v>
+        <v>481017</v>
       </c>
       <c r="R59" t="n">
-        <v>6787525</v>
+        <v>6787651</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7019,22 +7033,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7060,13 +7074,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112980896</t>
+          <t>https://artportalen.se/Sighting/112924074</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125106308</v>
+        <v>112980896</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -7095,19 +7109,25 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480781</v>
+        <v>480919</v>
       </c>
       <c r="R60" t="n">
-        <v>6787572</v>
+        <v>6787525</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7131,27 +7151,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Hackmärken färska i gran</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7166,27 +7181,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125106308</t>
+          <t>https://artportalen.se/Sighting/112980896</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112923064</v>
+        <v>125106308</v>
       </c>
       <c r="B61" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7194,47 +7209,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480817</v>
+        <v>480781</v>
       </c>
       <c r="R61" t="n">
-        <v>6787576</v>
+        <v>6787572</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7258,22 +7263,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Hackmärken färska i gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7288,24 +7298,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923064</t>
+          <t>https://artportalen.se/Sighting/125106308</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112982228</v>
+        <v>112923064</v>
       </c>
       <c r="B62" t="n">
         <v>58114</v>
@@ -7333,21 +7343,27 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480787</v>
+        <v>480817</v>
       </c>
       <c r="R62" t="n">
-        <v>6787755</v>
+        <v>6787576</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7374,22 +7390,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7409,66 +7425,64 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112982228</t>
+          <t>https://artportalen.se/Sighting/112923064</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112923140</v>
+        <v>112982228</v>
       </c>
       <c r="B63" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480817</v>
+        <v>480787</v>
       </c>
       <c r="R63" t="n">
-        <v>6787576</v>
+        <v>6787755</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7492,22 +7506,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7527,19 +7541,19 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923140</t>
+          <t>https://artportalen.se/Sighting/112982228</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112923512</v>
+        <v>112923140</v>
       </c>
       <c r="B64" t="n">
         <v>8455</v>
@@ -7580,13 +7594,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480733</v>
+        <v>480817</v>
       </c>
       <c r="R64" t="n">
-        <v>6787668</v>
+        <v>6787576</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7615,7 +7629,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7625,7 +7639,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7651,13 +7665,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923512</t>
+          <t>https://artportalen.se/Sighting/112923140</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112924028</v>
+        <v>112923512</v>
       </c>
       <c r="B65" t="n">
         <v>8455</v>
@@ -7687,19 +7701,24 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481017</v>
+        <v>480733</v>
       </c>
       <c r="R65" t="n">
-        <v>6787651</v>
+        <v>6787668</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7728,7 +7747,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7738,7 +7757,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7764,13 +7783,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924028</t>
+          <t>https://artportalen.se/Sighting/112923512</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112924151</v>
+        <v>112924028</v>
       </c>
       <c r="B66" t="n">
         <v>8455</v>
@@ -7802,17 +7821,17 @@
       <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480927</v>
+        <v>481017</v>
       </c>
       <c r="R66" t="n">
-        <v>6787699</v>
+        <v>6787651</v>
       </c>
       <c r="S66" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7841,7 +7860,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7851,7 +7870,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7877,13 +7896,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924151</t>
+          <t>https://artportalen.se/Sighting/112924028</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120747281</v>
+        <v>112924151</v>
       </c>
       <c r="B67" t="n">
         <v>8455</v>
@@ -7912,24 +7931,20 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480845</v>
+        <v>480927</v>
       </c>
       <c r="R67" t="n">
-        <v>6787659</v>
+        <v>6787699</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7953,17 +7968,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7972,31 +7992,30 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747281</t>
+          <t>https://artportalen.se/Sighting/112924151</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120747340</v>
+        <v>120747281</v>
       </c>
       <c r="B68" t="n">
         <v>8455</v>
@@ -8036,10 +8055,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480847</v>
+        <v>480845</v>
       </c>
       <c r="R68" t="n">
-        <v>6787707</v>
+        <v>6787659</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8103,63 +8122,56 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747340</t>
+          <t>https://artportalen.se/Sighting/120747281</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119568643</v>
+        <v>120747340</v>
       </c>
       <c r="B69" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481007</v>
+        <v>480847</v>
       </c>
       <c r="R69" t="n">
-        <v>6787620</v>
+        <v>6787707</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8186,12 +8198,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8207,27 +8224,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568643</t>
+          <t>https://artportalen.se/Sighting/120747340</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125187193</v>
+        <v>135708300</v>
       </c>
       <c r="B70" t="n">
-        <v>104628</v>
+        <v>8461</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8235,43 +8252,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222412</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480717</v>
+        <v>480839</v>
       </c>
       <c r="R70" t="n">
-        <v>6787597</v>
+        <v>6787636</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8298,12 +8311,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8314,66 +8337,88 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125187193</t>
+          <t>https://artportalen.se/Sighting/135708300</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112996021</v>
+        <v>119568643</v>
       </c>
       <c r="B71" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480899</v>
+        <v>481007</v>
       </c>
       <c r="R71" t="n">
-        <v>6787538</v>
+        <v>6787620</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8400,12 +8445,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8414,71 +8459,81 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996021</t>
+          <t>https://artportalen.se/Sighting/119568643</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121972913</v>
+        <v>125187193</v>
       </c>
       <c r="B72" t="n">
-        <v>79085</v>
+        <v>104628</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>222412</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480935</v>
+        <v>480717</v>
       </c>
       <c r="R72" t="n">
-        <v>6787807</v>
+        <v>6787597</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8502,12 +8557,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8522,27 +8577,27 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972913</t>
+          <t>https://artportalen.se/Sighting/125187193</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119568677</v>
+        <v>112996021</v>
       </c>
       <c r="B73" t="n">
-        <v>91402</v>
+        <v>79085</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8550,41 +8605,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>256703</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480971</v>
+        <v>480899</v>
       </c>
       <c r="R73" t="n">
-        <v>6787547</v>
+        <v>6787538</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8611,12 +8659,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8625,34 +8673,33 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568677</t>
+          <t>https://artportalen.se/Sighting/112996021</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120747144</v>
+        <v>121972913</v>
       </c>
       <c r="B74" t="n">
-        <v>79350</v>
+        <v>79085</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8660,37 +8707,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480904</v>
+        <v>480935</v>
       </c>
       <c r="R74" t="n">
-        <v>6787507</v>
+        <v>6787807</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8717,17 +8761,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8736,34 +8775,33 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747144</t>
+          <t>https://artportalen.se/Sighting/121972913</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120747368</v>
+        <v>119568677</v>
       </c>
       <c r="B75" t="n">
-        <v>79350</v>
+        <v>91402</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8771,37 +8809,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>260591</v>
+        <v>256703</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480840</v>
+        <v>480971</v>
       </c>
       <c r="R75" t="n">
-        <v>6787710</v>
+        <v>6787547</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8828,17 +8870,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>på tall</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8854,24 +8891,24 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747368</t>
+          <t>https://artportalen.se/Sighting/119568677</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125105944</v>
+        <v>120747144</v>
       </c>
       <c r="B76" t="n">
         <v>79350</v>
@@ -8900,19 +8937,22 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481003</v>
+        <v>480904</v>
       </c>
       <c r="R76" t="n">
-        <v>6787803</v>
+        <v>6787507</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8936,22 +8976,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8960,6 +8995,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8977,16 +9013,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125105944</t>
+          <t>https://artportalen.se/Sighting/120747144</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112989992</v>
+        <v>120747368</v>
       </c>
       <c r="B77" t="n">
-        <v>79359</v>
+        <v>79350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8994,21 +9030,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>260591</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9017,17 +9053,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481125</v>
+        <v>480840</v>
       </c>
       <c r="R77" t="n">
-        <v>6787708</v>
+        <v>6787710</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9051,17 +9087,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9082,22 +9118,22 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112989992</t>
+          <t>https://artportalen.se/Sighting/120747368</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121972885</v>
+        <v>125105944</v>
       </c>
       <c r="B78" t="n">
-        <v>91909</v>
+        <v>79350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9105,37 +9141,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>260591</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481124</v>
+        <v>481003</v>
       </c>
       <c r="R78" t="n">
-        <v>6787703</v>
+        <v>6787803</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9159,12 +9195,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9179,62 +9225,62 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972885</t>
+          <t>https://artportalen.se/Sighting/125105944</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121972895</v>
+        <v>135710473</v>
       </c>
       <c r="B79" t="n">
-        <v>93213</v>
+        <v>79461</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>260591</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481073</v>
+        <v>480848</v>
       </c>
       <c r="R79" t="n">
-        <v>6787790</v>
+        <v>6787635</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9261,12 +9307,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9281,65 +9342,68 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972895</t>
+          <t>https://artportalen.se/Sighting/135710473</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112996034</v>
+        <v>112989992</v>
       </c>
       <c r="B80" t="n">
-        <v>92281</v>
+        <v>79359</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2062</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481123</v>
+        <v>481125</v>
       </c>
       <c r="R80" t="n">
-        <v>6787706</v>
+        <v>6787708</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9371,39 +9435,45 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996034</t>
+          <t>https://artportalen.se/Sighting/112989992</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112996037</v>
+        <v>121972885</v>
       </c>
       <c r="B81" t="n">
-        <v>93197</v>
+        <v>91909</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9411,48 +9481,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481143</v>
+        <v>481124</v>
       </c>
       <c r="R81" t="n">
-        <v>6787609</v>
+        <v>6787703</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9476,12 +9535,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9490,83 +9549,71 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996037</t>
+          <t>https://artportalen.se/Sighting/121972885</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112996031</v>
+        <v>121972895</v>
       </c>
       <c r="B82" t="n">
-        <v>93209</v>
+        <v>93213</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481063</v>
+        <v>481073</v>
       </c>
       <c r="R82" t="n">
-        <v>6787744</v>
+        <v>6787790</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9590,12 +9637,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9610,68 +9657,65 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996031</t>
+          <t>https://artportalen.se/Sighting/121972895</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112990060</v>
+        <v>112996034</v>
       </c>
       <c r="B83" t="n">
-        <v>91930</v>
+        <v>92281</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5442</v>
+        <v>2062</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481141</v>
+        <v>481123</v>
       </c>
       <c r="R83" t="n">
-        <v>6787582</v>
+        <v>6787706</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9703,83 +9747,88 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112990060</t>
+          <t>https://artportalen.se/Sighting/112996034</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112996032</v>
+        <v>112996037</v>
       </c>
       <c r="B84" t="n">
-        <v>91282</v>
+        <v>93197</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481080</v>
+        <v>481143</v>
       </c>
       <c r="R84" t="n">
-        <v>6787730</v>
+        <v>6787609</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9817,6 +9866,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9834,54 +9884,65 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996032</t>
+          <t>https://artportalen.se/Sighting/112996037</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112996036</v>
+        <v>112996031</v>
       </c>
       <c r="B85" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481143</v>
+        <v>481063</v>
       </c>
       <c r="R85" t="n">
-        <v>6787598</v>
+        <v>6787744</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9936,16 +9997,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996036</t>
+          <t>https://artportalen.se/Sighting/112996031</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112983277</v>
+        <v>112990060</v>
       </c>
       <c r="B86" t="n">
-        <v>57953</v>
+        <v>91930</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9953,42 +10014,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481142</v>
+        <v>481141</v>
       </c>
       <c r="R86" t="n">
-        <v>6787700</v>
+        <v>6787582</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10018,19 +10074,14 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:20</t>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10039,33 +10090,34 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983277</t>
+          <t>https://artportalen.se/Sighting/112990060</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112983978</v>
+        <v>112996032</v>
       </c>
       <c r="B87" t="n">
-        <v>5179</v>
+        <v>91282</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10073,42 +10125,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100526</v>
+        <v>5685</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481104</v>
+        <v>481080</v>
       </c>
       <c r="R87" t="n">
-        <v>6787672</v>
+        <v>6787730</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10135,99 +10182,79 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983978</t>
+          <t>https://artportalen.se/Sighting/112996032</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112996035</v>
+        <v>112996036</v>
       </c>
       <c r="B88" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481128</v>
+        <v>481143</v>
       </c>
       <c r="R88" t="n">
-        <v>6787712</v>
+        <v>6787598</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10268,7 +10295,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10286,54 +10312,62 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996035</t>
+          <t>https://artportalen.se/Sighting/112996036</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121972923</v>
+        <v>112983277</v>
       </c>
       <c r="B89" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481148</v>
+        <v>481142</v>
       </c>
       <c r="R89" t="n">
         <v>6787700</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10357,12 +10391,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10377,27 +10421,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972923</t>
+          <t>https://artportalen.se/Sighting/112983277</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121972882</v>
+        <v>112983978</v>
       </c>
       <c r="B90" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10405,34 +10449,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481148</v>
+        <v>481104</v>
       </c>
       <c r="R90" t="n">
-        <v>6787700</v>
+        <v>6787672</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10459,12 +10508,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10473,33 +10532,34 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972882</t>
+          <t>https://artportalen.se/Sighting/112983978</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112983991</v>
+        <v>112996035</v>
       </c>
       <c r="B91" t="n">
-        <v>8455</v>
+        <v>5179</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10507,39 +10567,43 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481104</v>
+        <v>481128</v>
       </c>
       <c r="R91" t="n">
-        <v>6787672</v>
+        <v>6787712</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10569,19 +10633,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10597,49 +10651,49 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983991</t>
+          <t>https://artportalen.se/Sighting/112996035</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112996033</v>
+        <v>121972923</v>
       </c>
       <c r="B92" t="n">
-        <v>79085</v>
+        <v>5179</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>100526</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10649,10 +10703,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481079</v>
+        <v>481148</v>
       </c>
       <c r="R92" t="n">
-        <v>6787734</v>
+        <v>6787700</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10679,12 +10733,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10699,16 +10753,338 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972923</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>121972882</v>
+      </c>
+      <c r="B93" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>481148</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6787700</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972882</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>112983991</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>481104</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6787672</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983991</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>112996033</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>481079</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6787734</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112996033</t>
         </is>
@@ -10807,6 +11183,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ92"/>
+  <dimension ref="A1:AZ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112996024</v>
+        <v>135721948</v>
       </c>
       <c r="B8" t="n">
-        <v>92208</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,37 +1354,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480875</v>
+        <v>480816</v>
       </c>
       <c r="R8" t="n">
-        <v>6787485</v>
+        <v>6787643</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,12 +1408,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka ex på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,31 +1439,46 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996024</t>
+          <t>https://artportalen.se/Sighting/135721948</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119565457</v>
+        <v>112996024</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,39 +1486,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480985</v>
+        <v>480875</v>
       </c>
       <c r="R9" t="n">
-        <v>6787569</v>
+        <v>6787485</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,22 +1540,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,34 +1554,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565457</t>
+          <t>https://artportalen.se/Sighting/112996024</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95895917</v>
+        <v>119565457</v>
       </c>
       <c r="B10" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,44 +1588,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480826</v>
+        <v>480985</v>
       </c>
       <c r="R10" t="n">
-        <v>6787548</v>
+        <v>6787569</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,12 +1644,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,24 +1675,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95895917</t>
+          <t>https://artportalen.se/Sighting/119565457</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112996023</v>
+        <v>95895917</v>
       </c>
       <c r="B11" t="n">
         <v>92369</v>
@@ -1698,17 +1720,24 @@
           <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480874</v>
+        <v>480826</v>
       </c>
       <c r="R11" t="n">
-        <v>6787486</v>
+        <v>6787548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,12 +1764,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,71 +1778,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996023</t>
+          <t>https://artportalen.se/Sighting/95895917</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119342591</v>
+        <v>112996023</v>
       </c>
       <c r="B12" t="n">
-        <v>93206</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1439</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sammetstaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum martioflavum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480814</v>
+        <v>480874</v>
       </c>
       <c r="R12" t="n">
-        <v>6787531</v>
+        <v>6787486</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,22 +1867,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,68 +1887,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119342591</t>
+          <t>https://artportalen.se/Sighting/112996023</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119096505</v>
+        <v>119342591</v>
       </c>
       <c r="B13" t="n">
-        <v>91394</v>
+        <v>93206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2051</v>
+        <v>1439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Sammetstaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum martioflavum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480846</v>
+        <v>480814</v>
       </c>
       <c r="R13" t="n">
-        <v>6787516</v>
+        <v>6787531</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1957,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1976,14 +1993,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>I brant slänt på isälvssediment, mest gran i närheten, tall längre bort.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1993,22 +2004,22 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119096505</t>
+          <t>https://artportalen.se/Sighting/119342591</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112922790</v>
+        <v>119096505</v>
       </c>
       <c r="B14" t="n">
-        <v>93213</v>
+        <v>91394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,47 +2027,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480742</v>
+        <v>480846</v>
       </c>
       <c r="R14" t="n">
-        <v>6787676</v>
+        <v>6787516</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2080,22 +2084,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,30 +2108,36 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>I brant slänt på isälvssediment, mest gran i närheten, tall längre bort.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922790</t>
+          <t>https://artportalen.se/Sighting/119096505</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121972897</v>
+        <v>112922790</v>
       </c>
       <c r="B15" t="n">
         <v>93213</v>
@@ -2155,20 +2165,30 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481022</v>
+        <v>480742</v>
       </c>
       <c r="R15" t="n">
-        <v>6787739</v>
+        <v>6787676</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,12 +2212,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,24 +2242,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972897</t>
+          <t>https://artportalen.se/Sighting/112922790</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121972898</v>
+        <v>121972897</v>
       </c>
       <c r="B16" t="n">
         <v>93213</v>
@@ -2264,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480829</v>
+        <v>481022</v>
       </c>
       <c r="R16" t="n">
-        <v>6787731</v>
+        <v>6787739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,13 +2355,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972898</t>
+          <t>https://artportalen.se/Sighting/121972897</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121972901</v>
+        <v>121972898</v>
       </c>
       <c r="B17" t="n">
         <v>93213</v>
@@ -2366,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480745</v>
+        <v>480829</v>
       </c>
       <c r="R17" t="n">
-        <v>6787692</v>
+        <v>6787731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,38 +2457,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972901</t>
+          <t>https://artportalen.se/Sighting/121972898</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121972912</v>
+        <v>121972901</v>
       </c>
       <c r="B18" t="n">
-        <v>91962</v>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480966</v>
+        <v>480745</v>
       </c>
       <c r="R18" t="n">
-        <v>6787791</v>
+        <v>6787692</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,16 +2559,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972912</t>
+          <t>https://artportalen.se/Sighting/121972901</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121972884</v>
+        <v>121972912</v>
       </c>
       <c r="B19" t="n">
-        <v>87325</v>
+        <v>91962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,37 +2576,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3690</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480986</v>
+        <v>480966</v>
       </c>
       <c r="R19" t="n">
-        <v>6787836</v>
+        <v>6787791</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,11 +2638,6 @@
           <t>2024-09-03</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2639,16 +2661,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972884</t>
+          <t>https://artportalen.se/Sighting/121972912</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119096496</v>
+        <v>121972884</v>
       </c>
       <c r="B20" t="n">
-        <v>93189</v>
+        <v>87325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,17 +2701,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480846</v>
+        <v>480986</v>
       </c>
       <c r="R20" t="n">
-        <v>6787516</v>
+        <v>6787836</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2713,12 +2735,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2727,7 +2754,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2745,13 +2771,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119096496</t>
+          <t>https://artportalen.se/Sighting/121972884</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119565699</v>
+        <v>119096496</v>
       </c>
       <c r="B21" t="n">
         <v>93189</v>
@@ -2779,31 +2805,23 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480853</v>
+        <v>480846</v>
       </c>
       <c r="R21" t="n">
         <v>6787516</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2827,22 +2845,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,24 +2866,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565699</t>
+          <t>https://artportalen.se/Sighting/119096496</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119565742</v>
+        <v>119565699</v>
       </c>
       <c r="B22" t="n">
         <v>93189</v>
@@ -2905,7 +2913,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2917,14 +2925,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Siljansleden, Siljansleden, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480845</v>
+        <v>480853</v>
       </c>
       <c r="R22" t="n">
-        <v>6787511</v>
+        <v>6787516</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2956,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2966,7 +2974,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,13 +3001,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565742</t>
+          <t>https://artportalen.se/Sighting/119565699</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119566308</v>
+        <v>119565742</v>
       </c>
       <c r="B23" t="n">
         <v>93189</v>
@@ -3029,7 +3037,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3041,14 +3049,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Siljansleden, Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480816</v>
+        <v>480845</v>
       </c>
       <c r="R23" t="n">
-        <v>6787542</v>
+        <v>6787511</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3080,7 +3088,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3090,7 +3098,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3117,13 +3125,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119566308</t>
+          <t>https://artportalen.se/Sighting/119565742</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119568829</v>
+        <v>119566308</v>
       </c>
       <c r="B24" t="n">
         <v>93189</v>
@@ -3153,25 +3161,29 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480735</v>
+        <v>480816</v>
       </c>
       <c r="R24" t="n">
-        <v>6787658</v>
+        <v>6787542</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3198,9 +3210,19 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3216,24 +3238,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568829</t>
+          <t>https://artportalen.se/Sighting/119566308</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121972911</v>
+        <v>119568829</v>
       </c>
       <c r="B25" t="n">
         <v>93189</v>
@@ -3261,20 +3283,27 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480843</v>
+        <v>480735</v>
       </c>
       <c r="R25" t="n">
-        <v>6787540</v>
+        <v>6787658</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,12 +3327,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,33 +3341,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972911</t>
+          <t>https://artportalen.se/Sighting/119568829</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112922923</v>
+        <v>121972911</v>
       </c>
       <c r="B26" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3346,38 +3376,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480772</v>
+        <v>480843</v>
       </c>
       <c r="R26" t="n">
-        <v>6787679</v>
+        <v>6787540</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3401,22 +3430,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,24 +3450,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922923</t>
+          <t>https://artportalen.se/Sighting/121972911</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112922930</v>
+        <v>112922923</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3476,16 +3495,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3493,13 +3503,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480779</v>
+        <v>480772</v>
       </c>
       <c r="R27" t="n">
-        <v>6787677</v>
+        <v>6787679</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3528,7 +3538,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3538,7 +3548,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,13 +3574,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922930</t>
+          <t>https://artportalen.se/Sighting/112922923</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112923242</v>
+        <v>112922930</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3600,7 +3610,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3615,13 +3625,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480760</v>
+        <v>480779</v>
       </c>
       <c r="R28" t="n">
-        <v>6787645</v>
+        <v>6787677</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3650,7 +3660,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3660,7 +3670,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3686,13 +3696,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923242</t>
+          <t>https://artportalen.se/Sighting/112922930</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112996027</v>
+        <v>112923242</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3722,7 +3732,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3731,17 +3741,16 @@
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480947</v>
+        <v>480760</v>
       </c>
       <c r="R29" t="n">
-        <v>6787809</v>
+        <v>6787645</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3768,12 +3777,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3782,31 +3801,30 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996027</t>
+          <t>https://artportalen.se/Sighting/112923242</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112996030</v>
+        <v>112996027</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3836,7 +3854,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3852,10 +3870,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481005</v>
+        <v>480947</v>
       </c>
       <c r="R30" t="n">
-        <v>6787834</v>
+        <v>6787809</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3914,13 +3932,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996030</t>
+          <t>https://artportalen.se/Sighting/112996027</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119545661</v>
+        <v>112996030</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3948,8 +3966,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3958,13 +3984,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481008</v>
+        <v>481005</v>
       </c>
       <c r="R31" t="n">
-        <v>6787840</v>
+        <v>6787834</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3988,17 +4014,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>rikligt, tiotals</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,24 +4035,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119545661</t>
+          <t>https://artportalen.se/Sighting/112996030</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120837852</v>
+        <v>119545661</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -4059,16 +4080,8 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4077,13 +4090,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481001</v>
+        <v>481008</v>
       </c>
       <c r="R32" t="n">
-        <v>6787844</v>
+        <v>6787840</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4107,12 +4120,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>rikligt, tiotals</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,24 +4146,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120837852</t>
+          <t>https://artportalen.se/Sighting/119545661</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121972915</v>
+        <v>120837852</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4173,14 +4191,25 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480914</v>
+        <v>481001</v>
       </c>
       <c r="R33" t="n">
         <v>6787844</v>
@@ -4210,12 +4239,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,30 +4253,31 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972915</t>
+          <t>https://artportalen.se/Sighting/120837852</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121972916</v>
+        <v>121972915</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4282,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480915</v>
+        <v>480914</v>
       </c>
       <c r="R34" t="n">
-        <v>6787807</v>
+        <v>6787844</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,13 +4373,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972916</t>
+          <t>https://artportalen.se/Sighting/121972915</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121972917</v>
+        <v>121972916</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4384,10 +4414,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480797</v>
+        <v>480915</v>
       </c>
       <c r="R35" t="n">
-        <v>6787722</v>
+        <v>6787807</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4445,13 +4475,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972917</t>
+          <t>https://artportalen.se/Sighting/121972916</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121972918</v>
+        <v>121972917</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4486,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480812</v>
+        <v>480797</v>
       </c>
       <c r="R36" t="n">
-        <v>6787702</v>
+        <v>6787722</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4547,13 +4577,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972918</t>
+          <t>https://artportalen.se/Sighting/121972917</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121972919</v>
+        <v>121972918</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4588,10 +4618,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480773</v>
+        <v>480812</v>
       </c>
       <c r="R37" t="n">
-        <v>6787678</v>
+        <v>6787702</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4649,13 +4679,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972919</t>
+          <t>https://artportalen.se/Sighting/121972918</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121972920</v>
+        <v>121972919</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4690,10 +4720,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480994</v>
+        <v>480773</v>
       </c>
       <c r="R38" t="n">
-        <v>6787675</v>
+        <v>6787678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4751,13 +4781,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972920</t>
+          <t>https://artportalen.se/Sighting/121972919</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121972921</v>
+        <v>121972920</v>
       </c>
       <c r="B39" t="n">
         <v>93197</v>
@@ -4792,10 +4822,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480761</v>
+        <v>480994</v>
       </c>
       <c r="R39" t="n">
-        <v>6787650</v>
+        <v>6787675</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4853,13 +4883,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972921</t>
+          <t>https://artportalen.se/Sighting/121972920</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121972922</v>
+        <v>121972921</v>
       </c>
       <c r="B40" t="n">
         <v>93197</v>
@@ -4894,10 +4924,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480796</v>
+        <v>480761</v>
       </c>
       <c r="R40" t="n">
-        <v>6787645</v>
+        <v>6787650</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4955,13 +4985,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972922</t>
+          <t>https://artportalen.se/Sighting/121972921</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127640071</v>
+        <v>121972922</v>
       </c>
       <c r="B41" t="n">
         <v>93197</v>
@@ -4992,14 +5022,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480961</v>
+        <v>480796</v>
       </c>
       <c r="R41" t="n">
-        <v>6787858</v>
+        <v>6787645</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5026,12 +5056,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5046,27 +5076,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127640071</t>
+          <t>https://artportalen.se/Sighting/121972922</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121972907</v>
+        <v>127640071</v>
       </c>
       <c r="B42" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5074,34 +5104,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480936</v>
+        <v>480961</v>
       </c>
       <c r="R42" t="n">
-        <v>6787692</v>
+        <v>6787858</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5128,12 +5158,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5148,49 +5178,49 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972907</t>
+          <t>https://artportalen.se/Sighting/127640071</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112996025</v>
+        <v>121972907</v>
       </c>
       <c r="B43" t="n">
-        <v>91893</v>
+        <v>93209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4660</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5200,10 +5230,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480874</v>
+        <v>480936</v>
       </c>
       <c r="R43" t="n">
-        <v>6787479</v>
+        <v>6787692</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5230,12 +5260,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5250,72 +5280,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996025</t>
+          <t>https://artportalen.se/Sighting/121972907</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112996029</v>
+        <v>112996025</v>
       </c>
       <c r="B44" t="n">
-        <v>90522</v>
+        <v>91893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4962</v>
+        <v>4660</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481007</v>
+        <v>480874</v>
       </c>
       <c r="R44" t="n">
-        <v>6787835</v>
+        <v>6787479</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5370,16 +5393,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996029</t>
+          <t>https://artportalen.se/Sighting/112996025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112914094</v>
+        <v>112996029</v>
       </c>
       <c r="B45" t="n">
-        <v>91930</v>
+        <v>90522</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5387,37 +5410,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>4962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480743</v>
+        <v>481007</v>
       </c>
       <c r="R45" t="n">
-        <v>6787694</v>
+        <v>6787835</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5444,12 +5471,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5458,34 +5485,33 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914094</t>
+          <t>https://artportalen.se/Sighting/112996029</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112923898</v>
+        <v>112914094</v>
       </c>
       <c r="B46" t="n">
-        <v>93223</v>
+        <v>91930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5493,45 +5519,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480942</v>
+        <v>480743</v>
       </c>
       <c r="R46" t="n">
-        <v>6787720</v>
+        <v>6787694</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,22 +5576,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5589,27 +5597,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923898</t>
+          <t>https://artportalen.se/Sighting/112914094</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112996028</v>
+        <v>112923898</v>
       </c>
       <c r="B47" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5617,37 +5625,48 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480995</v>
+        <v>480942</v>
       </c>
       <c r="R47" t="n">
-        <v>6787829</v>
+        <v>6787720</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5671,12 +5690,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5685,71 +5714,69 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996028</t>
+          <t>https://artportalen.se/Sighting/112923898</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96117407</v>
+        <v>112996028</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480781</v>
+        <v>480995</v>
       </c>
       <c r="R48" t="n">
-        <v>6787572</v>
+        <v>6787829</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5776,12 +5803,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5790,46 +5817,30 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117407</t>
+          <t>https://artportalen.se/Sighting/112996028</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112914136</v>
+        <v>96117407</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5863,14 +5874,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480780</v>
+        <v>480781</v>
       </c>
       <c r="R49" t="n">
-        <v>6787640</v>
+        <v>6787572</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5897,17 +5908,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5920,6 +5926,21 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
@@ -5934,13 +5955,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914136</t>
+          <t>https://artportalen.se/Sighting/96117407</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112923198</v>
+        <v>112914136</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5969,20 +5990,22 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480817</v>
+        <v>480780</v>
       </c>
       <c r="R50" t="n">
-        <v>6787576</v>
+        <v>6787640</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6006,27 +6029,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6035,30 +6048,31 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923198</t>
+          <t>https://artportalen.se/Sighting/112914136</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112923608</v>
+        <v>112923198</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6094,13 +6108,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480882</v>
+        <v>480817</v>
       </c>
       <c r="R51" t="n">
-        <v>6787809</v>
+        <v>6787576</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6129,7 +6143,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6139,7 +6153,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6165,13 +6184,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923608</t>
+          <t>https://artportalen.se/Sighting/112923198</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112924155</v>
+        <v>112923608</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6207,13 +6226,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480927</v>
+        <v>480882</v>
       </c>
       <c r="R52" t="n">
-        <v>6787699</v>
+        <v>6787809</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6242,7 +6261,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6252,7 +6271,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6278,13 +6297,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924155</t>
+          <t>https://artportalen.se/Sighting/112923608</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120747170</v>
+        <v>112924155</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6313,22 +6332,20 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480886</v>
+        <v>480927</v>
       </c>
       <c r="R53" t="n">
-        <v>6787539</v>
+        <v>6787699</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6352,17 +6369,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6371,31 +6393,30 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747170</t>
+          <t>https://artportalen.se/Sighting/112924155</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120747198</v>
+        <v>120747170</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6433,10 +6454,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480878</v>
+        <v>480886</v>
       </c>
       <c r="R54" t="n">
-        <v>6787512</v>
+        <v>6787539</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6500,13 +6521,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747198</t>
+          <t>https://artportalen.se/Sighting/120747170</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120747228</v>
+        <v>120747198</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6544,10 +6565,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480890</v>
+        <v>480878</v>
       </c>
       <c r="R55" t="n">
-        <v>6787571</v>
+        <v>6787512</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6611,13 +6632,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747228</t>
+          <t>https://artportalen.se/Sighting/120747198</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120747402</v>
+        <v>120747228</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6655,10 +6676,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480831</v>
+        <v>480890</v>
       </c>
       <c r="R56" t="n">
-        <v>6787737</v>
+        <v>6787571</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6722,54 +6743,57 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747402</t>
+          <t>https://artportalen.se/Sighting/120747228</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112996022</v>
+        <v>120747402</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480891</v>
+        <v>480831</v>
       </c>
       <c r="R57" t="n">
-        <v>6787557</v>
+        <v>6787737</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6793,12 +6817,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6807,33 +6836,34 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996022</t>
+          <t>https://artportalen.se/Sighting/120747402</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112924074</v>
+        <v>112996022</v>
       </c>
       <c r="B58" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6841,43 +6871,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481017</v>
+        <v>480891</v>
       </c>
       <c r="R58" t="n">
-        <v>6787651</v>
+        <v>6787557</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6901,22 +6925,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6931,24 +6945,24 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924074</t>
+          <t>https://artportalen.se/Sighting/112996022</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112980896</v>
+        <v>112924074</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -6985,17 +6999,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480919</v>
+        <v>481017</v>
       </c>
       <c r="R59" t="n">
-        <v>6787525</v>
+        <v>6787651</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7019,22 +7033,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7060,13 +7074,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112980896</t>
+          <t>https://artportalen.se/Sighting/112924074</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125106308</v>
+        <v>112980896</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -7095,19 +7109,25 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480781</v>
+        <v>480919</v>
       </c>
       <c r="R60" t="n">
-        <v>6787572</v>
+        <v>6787525</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7131,27 +7151,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Hackmärken färska i gran</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7166,27 +7181,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125106308</t>
+          <t>https://artportalen.se/Sighting/112980896</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112923064</v>
+        <v>125106308</v>
       </c>
       <c r="B61" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7194,47 +7209,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480817</v>
+        <v>480781</v>
       </c>
       <c r="R61" t="n">
-        <v>6787576</v>
+        <v>6787572</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7258,22 +7263,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Hackmärken färska i gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7288,24 +7298,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923064</t>
+          <t>https://artportalen.se/Sighting/125106308</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112982228</v>
+        <v>112923064</v>
       </c>
       <c r="B62" t="n">
         <v>58114</v>
@@ -7333,21 +7343,27 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480787</v>
+        <v>480817</v>
       </c>
       <c r="R62" t="n">
-        <v>6787755</v>
+        <v>6787576</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7374,22 +7390,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7409,66 +7425,64 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112982228</t>
+          <t>https://artportalen.se/Sighting/112923064</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112923140</v>
+        <v>112982228</v>
       </c>
       <c r="B63" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480817</v>
+        <v>480787</v>
       </c>
       <c r="R63" t="n">
-        <v>6787576</v>
+        <v>6787755</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7492,22 +7506,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7527,19 +7541,19 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923140</t>
+          <t>https://artportalen.se/Sighting/112982228</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112923512</v>
+        <v>112923140</v>
       </c>
       <c r="B64" t="n">
         <v>8455</v>
@@ -7580,13 +7594,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480733</v>
+        <v>480817</v>
       </c>
       <c r="R64" t="n">
-        <v>6787668</v>
+        <v>6787576</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7615,7 +7629,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7625,7 +7639,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7651,13 +7665,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923512</t>
+          <t>https://artportalen.se/Sighting/112923140</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112924028</v>
+        <v>112923512</v>
       </c>
       <c r="B65" t="n">
         <v>8455</v>
@@ -7687,19 +7701,24 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481017</v>
+        <v>480733</v>
       </c>
       <c r="R65" t="n">
-        <v>6787651</v>
+        <v>6787668</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7728,7 +7747,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7738,7 +7757,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7764,13 +7783,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924028</t>
+          <t>https://artportalen.se/Sighting/112923512</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112924151</v>
+        <v>112924028</v>
       </c>
       <c r="B66" t="n">
         <v>8455</v>
@@ -7802,17 +7821,17 @@
       <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480927</v>
+        <v>481017</v>
       </c>
       <c r="R66" t="n">
-        <v>6787699</v>
+        <v>6787651</v>
       </c>
       <c r="S66" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7841,7 +7860,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7851,7 +7870,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7877,13 +7896,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924151</t>
+          <t>https://artportalen.se/Sighting/112924028</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120747281</v>
+        <v>112924151</v>
       </c>
       <c r="B67" t="n">
         <v>8455</v>
@@ -7912,24 +7931,20 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480845</v>
+        <v>480927</v>
       </c>
       <c r="R67" t="n">
-        <v>6787659</v>
+        <v>6787699</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7953,17 +7968,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7972,31 +7992,30 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747281</t>
+          <t>https://artportalen.se/Sighting/112924151</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120747340</v>
+        <v>120747281</v>
       </c>
       <c r="B68" t="n">
         <v>8455</v>
@@ -8036,10 +8055,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480847</v>
+        <v>480845</v>
       </c>
       <c r="R68" t="n">
-        <v>6787707</v>
+        <v>6787659</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8103,63 +8122,56 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747340</t>
+          <t>https://artportalen.se/Sighting/120747281</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119568643</v>
+        <v>120747340</v>
       </c>
       <c r="B69" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481007</v>
+        <v>480847</v>
       </c>
       <c r="R69" t="n">
-        <v>6787620</v>
+        <v>6787707</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8186,12 +8198,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8207,27 +8224,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568643</t>
+          <t>https://artportalen.se/Sighting/120747340</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125187193</v>
+        <v>135708300</v>
       </c>
       <c r="B70" t="n">
-        <v>104628</v>
+        <v>8461</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8235,43 +8252,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222412</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480717</v>
+        <v>480839</v>
       </c>
       <c r="R70" t="n">
-        <v>6787597</v>
+        <v>6787636</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8298,12 +8311,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8314,66 +8337,88 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125187193</t>
+          <t>https://artportalen.se/Sighting/135708300</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112996021</v>
+        <v>119568643</v>
       </c>
       <c r="B71" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480899</v>
+        <v>481007</v>
       </c>
       <c r="R71" t="n">
-        <v>6787538</v>
+        <v>6787620</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8400,12 +8445,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8414,71 +8459,81 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996021</t>
+          <t>https://artportalen.se/Sighting/119568643</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121972913</v>
+        <v>125187193</v>
       </c>
       <c r="B72" t="n">
-        <v>79085</v>
+        <v>104628</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>222412</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480935</v>
+        <v>480717</v>
       </c>
       <c r="R72" t="n">
-        <v>6787807</v>
+        <v>6787597</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8502,12 +8557,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8522,27 +8577,27 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972913</t>
+          <t>https://artportalen.se/Sighting/125187193</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119568677</v>
+        <v>112996021</v>
       </c>
       <c r="B73" t="n">
-        <v>91402</v>
+        <v>79085</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8550,41 +8605,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>256703</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480971</v>
+        <v>480899</v>
       </c>
       <c r="R73" t="n">
-        <v>6787547</v>
+        <v>6787538</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8611,12 +8659,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8625,34 +8673,33 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568677</t>
+          <t>https://artportalen.se/Sighting/112996021</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120747144</v>
+        <v>121972913</v>
       </c>
       <c r="B74" t="n">
-        <v>79350</v>
+        <v>79085</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8660,37 +8707,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480904</v>
+        <v>480935</v>
       </c>
       <c r="R74" t="n">
-        <v>6787507</v>
+        <v>6787807</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8717,17 +8761,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8736,34 +8775,33 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747144</t>
+          <t>https://artportalen.se/Sighting/121972913</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120747368</v>
+        <v>119568677</v>
       </c>
       <c r="B75" t="n">
-        <v>79350</v>
+        <v>91402</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8771,37 +8809,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>260591</v>
+        <v>256703</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480840</v>
+        <v>480971</v>
       </c>
       <c r="R75" t="n">
-        <v>6787710</v>
+        <v>6787547</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8828,17 +8870,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>på tall</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8854,24 +8891,24 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747368</t>
+          <t>https://artportalen.se/Sighting/119568677</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125105944</v>
+        <v>120747144</v>
       </c>
       <c r="B76" t="n">
         <v>79350</v>
@@ -8900,19 +8937,22 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481003</v>
+        <v>480904</v>
       </c>
       <c r="R76" t="n">
-        <v>6787803</v>
+        <v>6787507</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8936,22 +8976,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8960,6 +8995,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8977,16 +9013,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125105944</t>
+          <t>https://artportalen.se/Sighting/120747144</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112989992</v>
+        <v>120747368</v>
       </c>
       <c r="B77" t="n">
-        <v>79359</v>
+        <v>79350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8994,21 +9030,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>260591</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9017,17 +9053,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481125</v>
+        <v>480840</v>
       </c>
       <c r="R77" t="n">
-        <v>6787708</v>
+        <v>6787710</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9051,17 +9087,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9082,22 +9118,22 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112989992</t>
+          <t>https://artportalen.se/Sighting/120747368</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121972885</v>
+        <v>125105944</v>
       </c>
       <c r="B78" t="n">
-        <v>91909</v>
+        <v>79350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9105,37 +9141,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>260591</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481124</v>
+        <v>481003</v>
       </c>
       <c r="R78" t="n">
-        <v>6787703</v>
+        <v>6787803</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9159,12 +9195,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9179,62 +9225,62 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972885</t>
+          <t>https://artportalen.se/Sighting/125105944</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121972895</v>
+        <v>135710473</v>
       </c>
       <c r="B79" t="n">
-        <v>93213</v>
+        <v>79464</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>260591</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481073</v>
+        <v>480848</v>
       </c>
       <c r="R79" t="n">
-        <v>6787790</v>
+        <v>6787635</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9261,12 +9307,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9281,65 +9342,68 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972895</t>
+          <t>https://artportalen.se/Sighting/135710473</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112996034</v>
+        <v>112989992</v>
       </c>
       <c r="B80" t="n">
-        <v>92281</v>
+        <v>79359</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2062</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481123</v>
+        <v>481125</v>
       </c>
       <c r="R80" t="n">
-        <v>6787706</v>
+        <v>6787708</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9371,39 +9435,45 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996034</t>
+          <t>https://artportalen.se/Sighting/112989992</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112996037</v>
+        <v>121972885</v>
       </c>
       <c r="B81" t="n">
-        <v>93197</v>
+        <v>91909</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9411,48 +9481,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481143</v>
+        <v>481124</v>
       </c>
       <c r="R81" t="n">
-        <v>6787609</v>
+        <v>6787703</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9476,12 +9535,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9490,83 +9549,71 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996037</t>
+          <t>https://artportalen.se/Sighting/121972885</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112996031</v>
+        <v>121972895</v>
       </c>
       <c r="B82" t="n">
-        <v>93209</v>
+        <v>93213</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481063</v>
+        <v>481073</v>
       </c>
       <c r="R82" t="n">
-        <v>6787744</v>
+        <v>6787790</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9590,12 +9637,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9610,68 +9657,65 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996031</t>
+          <t>https://artportalen.se/Sighting/121972895</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112990060</v>
+        <v>112996034</v>
       </c>
       <c r="B83" t="n">
-        <v>91930</v>
+        <v>92281</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5442</v>
+        <v>2062</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481141</v>
+        <v>481123</v>
       </c>
       <c r="R83" t="n">
-        <v>6787582</v>
+        <v>6787706</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9703,83 +9747,88 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112990060</t>
+          <t>https://artportalen.se/Sighting/112996034</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112996032</v>
+        <v>112996037</v>
       </c>
       <c r="B84" t="n">
-        <v>91282</v>
+        <v>93197</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481080</v>
+        <v>481143</v>
       </c>
       <c r="R84" t="n">
-        <v>6787730</v>
+        <v>6787609</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9817,6 +9866,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9834,54 +9884,65 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996032</t>
+          <t>https://artportalen.se/Sighting/112996037</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112996036</v>
+        <v>112996031</v>
       </c>
       <c r="B85" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481143</v>
+        <v>481063</v>
       </c>
       <c r="R85" t="n">
-        <v>6787598</v>
+        <v>6787744</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9936,16 +9997,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996036</t>
+          <t>https://artportalen.se/Sighting/112996031</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112983277</v>
+        <v>112990060</v>
       </c>
       <c r="B86" t="n">
-        <v>57953</v>
+        <v>91930</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9953,42 +10014,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481142</v>
+        <v>481141</v>
       </c>
       <c r="R86" t="n">
-        <v>6787700</v>
+        <v>6787582</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10018,19 +10074,14 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:20</t>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10039,33 +10090,34 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983277</t>
+          <t>https://artportalen.se/Sighting/112990060</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112983978</v>
+        <v>112996032</v>
       </c>
       <c r="B87" t="n">
-        <v>5179</v>
+        <v>91282</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10073,42 +10125,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100526</v>
+        <v>5685</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481104</v>
+        <v>481080</v>
       </c>
       <c r="R87" t="n">
-        <v>6787672</v>
+        <v>6787730</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10135,99 +10182,79 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983978</t>
+          <t>https://artportalen.se/Sighting/112996032</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112996035</v>
+        <v>112996036</v>
       </c>
       <c r="B88" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481128</v>
+        <v>481143</v>
       </c>
       <c r="R88" t="n">
-        <v>6787712</v>
+        <v>6787598</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10268,7 +10295,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10286,54 +10312,62 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996035</t>
+          <t>https://artportalen.se/Sighting/112996036</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121972923</v>
+        <v>112983277</v>
       </c>
       <c r="B89" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481148</v>
+        <v>481142</v>
       </c>
       <c r="R89" t="n">
         <v>6787700</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10357,12 +10391,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10377,27 +10421,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972923</t>
+          <t>https://artportalen.se/Sighting/112983277</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121972882</v>
+        <v>112983978</v>
       </c>
       <c r="B90" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10405,34 +10449,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481148</v>
+        <v>481104</v>
       </c>
       <c r="R90" t="n">
-        <v>6787700</v>
+        <v>6787672</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10459,12 +10508,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10473,33 +10532,34 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972882</t>
+          <t>https://artportalen.se/Sighting/112983978</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112983991</v>
+        <v>112996035</v>
       </c>
       <c r="B91" t="n">
-        <v>8455</v>
+        <v>5179</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10507,39 +10567,43 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481104</v>
+        <v>481128</v>
       </c>
       <c r="R91" t="n">
-        <v>6787672</v>
+        <v>6787712</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10569,19 +10633,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10597,49 +10651,49 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983991</t>
+          <t>https://artportalen.se/Sighting/112996035</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112996033</v>
+        <v>121972923</v>
       </c>
       <c r="B92" t="n">
-        <v>79085</v>
+        <v>5179</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>100526</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10649,10 +10703,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481079</v>
+        <v>481148</v>
       </c>
       <c r="R92" t="n">
-        <v>6787734</v>
+        <v>6787700</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10679,12 +10733,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10699,16 +10753,338 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972923</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>121972882</v>
+      </c>
+      <c r="B93" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>481148</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6787700</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972882</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>112983991</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>481104</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6787672</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983991</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>112996033</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>481079</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6787734</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112996033</t>
         </is>
@@ -10807,6 +11183,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>135721948</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>135708300</v>
       </c>
       <c r="B70" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>135710473</v>
       </c>
       <c r="B79" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>135721948</v>
       </c>
       <c r="B8" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>135710473</v>
       </c>
       <c r="B79" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>135721948</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>135710473</v>
       </c>
       <c r="B79" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>135721948</v>
       </c>
       <c r="B8" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>135710473</v>
       </c>
       <c r="B79" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>135721948</v>
       </c>
       <c r="B8" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>135710473</v>
       </c>
       <c r="B79" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>135721948</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>135710473</v>
       </c>
       <c r="B79" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ95"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2565,45 +2565,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121972912</v>
+        <v>136457415</v>
       </c>
       <c r="B19" t="n">
-        <v>91962</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>SV Ekentjärn, SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480966</v>
+        <v>480744</v>
       </c>
       <c r="R19" t="n">
-        <v>6787791</v>
+        <v>6787688</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,12 +2630,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,27 +2660,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972912</t>
+          <t>https://artportalen.se/Sighting/136457415</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121972884</v>
+        <v>121972912</v>
       </c>
       <c r="B20" t="n">
-        <v>87325</v>
+        <v>91962</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,37 +2688,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3690</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480986</v>
+        <v>480966</v>
       </c>
       <c r="R20" t="n">
-        <v>6787836</v>
+        <v>6787791</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2743,11 +2750,6 @@
           <t>2024-09-03</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2771,16 +2773,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972884</t>
+          <t>https://artportalen.se/Sighting/121972912</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119096496</v>
+        <v>121972884</v>
       </c>
       <c r="B21" t="n">
-        <v>93189</v>
+        <v>87325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,21 +2790,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,17 +2813,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480846</v>
+        <v>480986</v>
       </c>
       <c r="R21" t="n">
-        <v>6787516</v>
+        <v>6787836</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2845,12 +2847,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,7 +2866,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2877,13 +2883,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119096496</t>
+          <t>https://artportalen.se/Sighting/121972884</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119565699</v>
+        <v>119096496</v>
       </c>
       <c r="B22" t="n">
         <v>93189</v>
@@ -2911,31 +2917,23 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480853</v>
+        <v>480846</v>
       </c>
       <c r="R22" t="n">
         <v>6787516</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2959,22 +2957,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,24 +2978,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565699</t>
+          <t>https://artportalen.se/Sighting/119096496</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119565742</v>
+        <v>119565699</v>
       </c>
       <c r="B23" t="n">
         <v>93189</v>
@@ -3037,7 +3025,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3049,14 +3037,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Siljansleden, Siljansleden, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480845</v>
+        <v>480853</v>
       </c>
       <c r="R23" t="n">
-        <v>6787511</v>
+        <v>6787516</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3088,7 +3076,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3098,7 +3086,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,13 +3113,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565742</t>
+          <t>https://artportalen.se/Sighting/119565699</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119566308</v>
+        <v>119565742</v>
       </c>
       <c r="B24" t="n">
         <v>93189</v>
@@ -3161,7 +3149,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3173,14 +3161,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Siljansleden, Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480816</v>
+        <v>480845</v>
       </c>
       <c r="R24" t="n">
-        <v>6787542</v>
+        <v>6787511</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3212,7 +3200,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3222,7 +3210,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,13 +3237,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119566308</t>
+          <t>https://artportalen.se/Sighting/119565742</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119568829</v>
+        <v>119566308</v>
       </c>
       <c r="B25" t="n">
         <v>93189</v>
@@ -3285,25 +3273,29 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480735</v>
+        <v>480816</v>
       </c>
       <c r="R25" t="n">
-        <v>6787658</v>
+        <v>6787542</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,9 +3322,19 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,24 +3350,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568829</t>
+          <t>https://artportalen.se/Sighting/119566308</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121972911</v>
+        <v>119568829</v>
       </c>
       <c r="B26" t="n">
         <v>93189</v>
@@ -3393,20 +3395,27 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480843</v>
+        <v>480735</v>
       </c>
       <c r="R26" t="n">
-        <v>6787540</v>
+        <v>6787658</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3430,12 +3439,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3444,33 +3453,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972911</t>
+          <t>https://artportalen.se/Sighting/119568829</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112922923</v>
+        <v>121972911</v>
       </c>
       <c r="B27" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,38 +3488,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480772</v>
+        <v>480843</v>
       </c>
       <c r="R27" t="n">
-        <v>6787679</v>
+        <v>6787540</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3533,22 +3542,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3563,24 +3562,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922923</t>
+          <t>https://artportalen.se/Sighting/121972911</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112922930</v>
+        <v>112922923</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3608,16 +3607,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3625,13 +3615,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480779</v>
+        <v>480772</v>
       </c>
       <c r="R28" t="n">
-        <v>6787677</v>
+        <v>6787679</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3660,7 +3650,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3670,7 +3660,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3696,13 +3686,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922930</t>
+          <t>https://artportalen.se/Sighting/112922923</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112923242</v>
+        <v>112922930</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3732,7 +3722,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3747,13 +3737,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480760</v>
+        <v>480779</v>
       </c>
       <c r="R29" t="n">
-        <v>6787645</v>
+        <v>6787677</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,7 +3772,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3792,7 +3782,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,13 +3808,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923242</t>
+          <t>https://artportalen.se/Sighting/112922930</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112996027</v>
+        <v>112923242</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3854,7 +3844,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3863,17 +3853,16 @@
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480947</v>
+        <v>480760</v>
       </c>
       <c r="R30" t="n">
-        <v>6787809</v>
+        <v>6787645</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3900,12 +3889,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3914,31 +3913,30 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996027</t>
+          <t>https://artportalen.se/Sighting/112923242</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112996030</v>
+        <v>112996027</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3968,7 +3966,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3984,10 +3982,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481005</v>
+        <v>480947</v>
       </c>
       <c r="R31" t="n">
-        <v>6787834</v>
+        <v>6787809</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4046,13 +4044,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996030</t>
+          <t>https://artportalen.se/Sighting/112996027</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119545661</v>
+        <v>112996030</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -4080,8 +4078,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4090,13 +4096,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481008</v>
+        <v>481005</v>
       </c>
       <c r="R32" t="n">
-        <v>6787840</v>
+        <v>6787834</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4120,17 +4126,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>rikligt, tiotals</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4146,24 +4147,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119545661</t>
+          <t>https://artportalen.se/Sighting/112996030</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120837852</v>
+        <v>119545661</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4191,16 +4192,8 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4209,13 +4202,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481001</v>
+        <v>481008</v>
       </c>
       <c r="R33" t="n">
-        <v>6787844</v>
+        <v>6787840</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4239,12 +4232,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>rikligt, tiotals</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4260,24 +4258,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120837852</t>
+          <t>https://artportalen.se/Sighting/119545661</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121972915</v>
+        <v>120837852</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4305,14 +4303,25 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480914</v>
+        <v>481001</v>
       </c>
       <c r="R34" t="n">
         <v>6787844</v>
@@ -4342,12 +4351,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,30 +4365,31 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972915</t>
+          <t>https://artportalen.se/Sighting/120837852</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121972916</v>
+        <v>121972915</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4414,10 +4424,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480915</v>
+        <v>480914</v>
       </c>
       <c r="R35" t="n">
-        <v>6787807</v>
+        <v>6787844</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,13 +4485,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972916</t>
+          <t>https://artportalen.se/Sighting/121972915</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121972917</v>
+        <v>121972916</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4516,10 +4526,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480797</v>
+        <v>480915</v>
       </c>
       <c r="R36" t="n">
-        <v>6787722</v>
+        <v>6787807</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4577,13 +4587,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972917</t>
+          <t>https://artportalen.se/Sighting/121972916</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121972918</v>
+        <v>121972917</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4618,10 +4628,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480812</v>
+        <v>480797</v>
       </c>
       <c r="R37" t="n">
-        <v>6787702</v>
+        <v>6787722</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4679,13 +4689,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972918</t>
+          <t>https://artportalen.se/Sighting/121972917</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121972919</v>
+        <v>121972918</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4720,10 +4730,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480773</v>
+        <v>480812</v>
       </c>
       <c r="R38" t="n">
-        <v>6787678</v>
+        <v>6787702</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4781,13 +4791,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972919</t>
+          <t>https://artportalen.se/Sighting/121972918</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121972920</v>
+        <v>121972919</v>
       </c>
       <c r="B39" t="n">
         <v>93197</v>
@@ -4822,10 +4832,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480994</v>
+        <v>480773</v>
       </c>
       <c r="R39" t="n">
-        <v>6787675</v>
+        <v>6787678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4883,13 +4893,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972920</t>
+          <t>https://artportalen.se/Sighting/121972919</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121972921</v>
+        <v>121972920</v>
       </c>
       <c r="B40" t="n">
         <v>93197</v>
@@ -4924,10 +4934,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480761</v>
+        <v>480994</v>
       </c>
       <c r="R40" t="n">
-        <v>6787650</v>
+        <v>6787675</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4985,13 +4995,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972921</t>
+          <t>https://artportalen.se/Sighting/121972920</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121972922</v>
+        <v>121972921</v>
       </c>
       <c r="B41" t="n">
         <v>93197</v>
@@ -5026,10 +5036,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480796</v>
+        <v>480761</v>
       </c>
       <c r="R41" t="n">
-        <v>6787645</v>
+        <v>6787650</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5087,13 +5097,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972922</t>
+          <t>https://artportalen.se/Sighting/121972921</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127640071</v>
+        <v>121972922</v>
       </c>
       <c r="B42" t="n">
         <v>93197</v>
@@ -5124,14 +5134,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480961</v>
+        <v>480796</v>
       </c>
       <c r="R42" t="n">
-        <v>6787858</v>
+        <v>6787645</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5158,12 +5168,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5178,27 +5188,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127640071</t>
+          <t>https://artportalen.se/Sighting/121972922</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121972907</v>
+        <v>127640071</v>
       </c>
       <c r="B43" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5206,34 +5216,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480936</v>
+        <v>480961</v>
       </c>
       <c r="R43" t="n">
-        <v>6787692</v>
+        <v>6787858</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5260,12 +5270,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,49 +5290,49 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972907</t>
+          <t>https://artportalen.se/Sighting/127640071</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112996025</v>
+        <v>121972907</v>
       </c>
       <c r="B44" t="n">
-        <v>91893</v>
+        <v>93209</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4660</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5332,10 +5342,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480874</v>
+        <v>480936</v>
       </c>
       <c r="R44" t="n">
-        <v>6787479</v>
+        <v>6787692</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5362,12 +5372,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5382,72 +5392,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996025</t>
+          <t>https://artportalen.se/Sighting/121972907</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112996029</v>
+        <v>112996025</v>
       </c>
       <c r="B45" t="n">
-        <v>90522</v>
+        <v>91893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4962</v>
+        <v>4660</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481007</v>
+        <v>480874</v>
       </c>
       <c r="R45" t="n">
-        <v>6787835</v>
+        <v>6787479</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5502,16 +5505,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996029</t>
+          <t>https://artportalen.se/Sighting/112996025</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112914094</v>
+        <v>112996029</v>
       </c>
       <c r="B46" t="n">
-        <v>91930</v>
+        <v>90522</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5519,37 +5522,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>4962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480743</v>
+        <v>481007</v>
       </c>
       <c r="R46" t="n">
-        <v>6787694</v>
+        <v>6787835</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5576,12 +5583,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5590,34 +5597,33 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914094</t>
+          <t>https://artportalen.se/Sighting/112996029</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112923898</v>
+        <v>112914094</v>
       </c>
       <c r="B47" t="n">
-        <v>93223</v>
+        <v>91930</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5625,45 +5631,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480942</v>
+        <v>480743</v>
       </c>
       <c r="R47" t="n">
-        <v>6787720</v>
+        <v>6787694</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5690,22 +5688,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5721,27 +5709,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923898</t>
+          <t>https://artportalen.se/Sighting/112914094</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112996028</v>
+        <v>112923898</v>
       </c>
       <c r="B48" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5749,37 +5737,48 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480995</v>
+        <v>480942</v>
       </c>
       <c r="R48" t="n">
-        <v>6787829</v>
+        <v>6787720</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5803,12 +5802,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5817,71 +5826,69 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996028</t>
+          <t>https://artportalen.se/Sighting/112923898</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>96117407</v>
+        <v>112996028</v>
       </c>
       <c r="B49" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480781</v>
+        <v>480995</v>
       </c>
       <c r="R49" t="n">
-        <v>6787572</v>
+        <v>6787829</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5908,12 +5915,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5922,46 +5929,30 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117407</t>
+          <t>https://artportalen.se/Sighting/112996028</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112914136</v>
+        <v>96117407</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5995,14 +5986,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480780</v>
+        <v>480781</v>
       </c>
       <c r="R50" t="n">
-        <v>6787640</v>
+        <v>6787572</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6029,17 +6020,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6052,6 +6038,21 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
@@ -6066,13 +6067,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914136</t>
+          <t>https://artportalen.se/Sighting/96117407</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112923198</v>
+        <v>112914136</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6101,20 +6102,22 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480817</v>
+        <v>480780</v>
       </c>
       <c r="R51" t="n">
-        <v>6787576</v>
+        <v>6787640</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6138,27 +6141,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6167,30 +6160,31 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923198</t>
+          <t>https://artportalen.se/Sighting/112914136</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112923608</v>
+        <v>112923198</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6226,13 +6220,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480882</v>
+        <v>480817</v>
       </c>
       <c r="R52" t="n">
-        <v>6787809</v>
+        <v>6787576</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6261,7 +6255,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6271,7 +6265,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6297,13 +6296,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923608</t>
+          <t>https://artportalen.se/Sighting/112923198</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112924155</v>
+        <v>112923608</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6339,13 +6338,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480927</v>
+        <v>480882</v>
       </c>
       <c r="R53" t="n">
-        <v>6787699</v>
+        <v>6787809</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6374,7 +6373,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6384,7 +6383,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6410,13 +6409,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924155</t>
+          <t>https://artportalen.se/Sighting/112923608</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120747170</v>
+        <v>112924155</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6445,22 +6444,20 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480886</v>
+        <v>480927</v>
       </c>
       <c r="R54" t="n">
-        <v>6787539</v>
+        <v>6787699</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6484,17 +6481,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6503,31 +6505,30 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747170</t>
+          <t>https://artportalen.se/Sighting/112924155</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120747198</v>
+        <v>120747170</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6565,10 +6566,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480878</v>
+        <v>480886</v>
       </c>
       <c r="R55" t="n">
-        <v>6787512</v>
+        <v>6787539</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6632,13 +6633,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747198</t>
+          <t>https://artportalen.se/Sighting/120747170</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120747228</v>
+        <v>120747198</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6676,10 +6677,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480890</v>
+        <v>480878</v>
       </c>
       <c r="R56" t="n">
-        <v>6787571</v>
+        <v>6787512</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6743,13 +6744,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747228</t>
+          <t>https://artportalen.se/Sighting/120747198</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120747402</v>
+        <v>120747228</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6787,10 +6788,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480831</v>
+        <v>480890</v>
       </c>
       <c r="R57" t="n">
-        <v>6787737</v>
+        <v>6787571</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6854,54 +6855,57 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747402</t>
+          <t>https://artportalen.se/Sighting/120747228</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112996022</v>
+        <v>120747402</v>
       </c>
       <c r="B58" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480891</v>
+        <v>480831</v>
       </c>
       <c r="R58" t="n">
-        <v>6787557</v>
+        <v>6787737</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6925,12 +6929,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6939,33 +6948,34 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996022</t>
+          <t>https://artportalen.se/Sighting/120747402</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112924074</v>
+        <v>112996022</v>
       </c>
       <c r="B59" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6973,43 +6983,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481017</v>
+        <v>480891</v>
       </c>
       <c r="R59" t="n">
-        <v>6787651</v>
+        <v>6787557</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7033,22 +7037,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,24 +7057,24 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924074</t>
+          <t>https://artportalen.se/Sighting/112996022</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112980896</v>
+        <v>112924074</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -7117,17 +7111,17 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480919</v>
+        <v>481017</v>
       </c>
       <c r="R60" t="n">
-        <v>6787525</v>
+        <v>6787651</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7151,22 +7145,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7192,13 +7186,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112980896</t>
+          <t>https://artportalen.se/Sighting/112924074</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125106308</v>
+        <v>112980896</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -7227,19 +7221,25 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480781</v>
+        <v>480919</v>
       </c>
       <c r="R61" t="n">
-        <v>6787572</v>
+        <v>6787525</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7263,27 +7263,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Hackmärken färska i gran</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7298,27 +7293,27 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125106308</t>
+          <t>https://artportalen.se/Sighting/112980896</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112923064</v>
+        <v>125106308</v>
       </c>
       <c r="B62" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7326,47 +7321,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480817</v>
+        <v>480781</v>
       </c>
       <c r="R62" t="n">
-        <v>6787576</v>
+        <v>6787572</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7390,22 +7375,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Hackmärken färska i gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7420,24 +7410,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923064</t>
+          <t>https://artportalen.se/Sighting/125106308</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112982228</v>
+        <v>112923064</v>
       </c>
       <c r="B63" t="n">
         <v>58114</v>
@@ -7465,21 +7455,27 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480787</v>
+        <v>480817</v>
       </c>
       <c r="R63" t="n">
-        <v>6787755</v>
+        <v>6787576</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7506,22 +7502,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7541,66 +7537,64 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112982228</t>
+          <t>https://artportalen.se/Sighting/112923064</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112923140</v>
+        <v>112982228</v>
       </c>
       <c r="B64" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480817</v>
+        <v>480787</v>
       </c>
       <c r="R64" t="n">
-        <v>6787576</v>
+        <v>6787755</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7624,22 +7618,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7659,19 +7653,19 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923140</t>
+          <t>https://artportalen.se/Sighting/112982228</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112923512</v>
+        <v>112923140</v>
       </c>
       <c r="B65" t="n">
         <v>8455</v>
@@ -7712,13 +7706,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480733</v>
+        <v>480817</v>
       </c>
       <c r="R65" t="n">
-        <v>6787668</v>
+        <v>6787576</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7747,7 +7741,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7757,7 +7751,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7783,13 +7777,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923512</t>
+          <t>https://artportalen.se/Sighting/112923140</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112924028</v>
+        <v>112923512</v>
       </c>
       <c r="B66" t="n">
         <v>8455</v>
@@ -7819,19 +7813,24 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481017</v>
+        <v>480733</v>
       </c>
       <c r="R66" t="n">
-        <v>6787651</v>
+        <v>6787668</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7860,7 +7859,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7870,7 +7869,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7896,13 +7895,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924028</t>
+          <t>https://artportalen.se/Sighting/112923512</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112924151</v>
+        <v>112924028</v>
       </c>
       <c r="B67" t="n">
         <v>8455</v>
@@ -7934,17 +7933,17 @@
       <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480927</v>
+        <v>481017</v>
       </c>
       <c r="R67" t="n">
-        <v>6787699</v>
+        <v>6787651</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7973,7 +7972,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7983,7 +7982,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8009,13 +8008,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924151</t>
+          <t>https://artportalen.se/Sighting/112924028</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120747281</v>
+        <v>112924151</v>
       </c>
       <c r="B68" t="n">
         <v>8455</v>
@@ -8044,24 +8043,20 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480845</v>
+        <v>480927</v>
       </c>
       <c r="R68" t="n">
-        <v>6787659</v>
+        <v>6787699</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8085,17 +8080,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8104,31 +8104,30 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747281</t>
+          <t>https://artportalen.se/Sighting/112924151</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120747340</v>
+        <v>120747281</v>
       </c>
       <c r="B69" t="n">
         <v>8455</v>
@@ -8168,10 +8167,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480847</v>
+        <v>480845</v>
       </c>
       <c r="R69" t="n">
-        <v>6787707</v>
+        <v>6787659</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8235,16 +8234,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747340</t>
+          <t>https://artportalen.se/Sighting/120747281</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135708300</v>
+        <v>120747340</v>
       </c>
       <c r="B70" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8270,24 +8269,24 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480839</v>
+        <v>480847</v>
       </c>
       <c r="R70" t="n">
-        <v>6787636</v>
+        <v>6787707</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8311,22 +8310,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>08:59</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>08:59</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8335,18 +8329,9 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8362,66 +8347,59 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708300</t>
+          <t>https://artportalen.se/Sighting/120747340</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119568643</v>
+        <v>135708300</v>
       </c>
       <c r="B71" t="n">
-        <v>99118</v>
+        <v>8463</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481007</v>
+        <v>480839</v>
       </c>
       <c r="R71" t="n">
-        <v>6787620</v>
+        <v>6787636</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8445,12 +8423,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8459,61 +8447,70 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568643</t>
+          <t>https://artportalen.se/Sighting/135708300</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125187193</v>
+        <v>119568643</v>
       </c>
       <c r="B72" t="n">
-        <v>104628</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8521,19 +8518,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480717</v>
+        <v>481007</v>
       </c>
       <c r="R72" t="n">
-        <v>6787597</v>
+        <v>6787620</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8557,12 +8557,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8571,6 +8571,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8582,60 +8583,69 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125187193</t>
+          <t>https://artportalen.se/Sighting/119568643</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112996021</v>
+        <v>125187193</v>
       </c>
       <c r="B73" t="n">
-        <v>79085</v>
+        <v>104628</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>222412</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480899</v>
+        <v>480717</v>
       </c>
       <c r="R73" t="n">
-        <v>6787538</v>
+        <v>6787597</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8659,12 +8669,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8679,24 +8689,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996021</t>
+          <t>https://artportalen.se/Sighting/125187193</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121972913</v>
+        <v>112996021</v>
       </c>
       <c r="B74" t="n">
         <v>79085</v>
@@ -8731,10 +8741,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480935</v>
+        <v>480899</v>
       </c>
       <c r="R74" t="n">
-        <v>6787807</v>
+        <v>6787538</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8761,12 +8771,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8781,27 +8791,27 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972913</t>
+          <t>https://artportalen.se/Sighting/112996021</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119568677</v>
+        <v>121972913</v>
       </c>
       <c r="B75" t="n">
-        <v>91402</v>
+        <v>79085</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8809,41 +8819,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>256703</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480971</v>
+        <v>480935</v>
       </c>
       <c r="R75" t="n">
-        <v>6787547</v>
+        <v>6787807</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8870,12 +8873,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8884,34 +8887,33 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568677</t>
+          <t>https://artportalen.se/Sighting/121972913</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120747144</v>
+        <v>119568677</v>
       </c>
       <c r="B76" t="n">
-        <v>79350</v>
+        <v>91402</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8919,37 +8921,41 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>260591</v>
+        <v>256703</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480904</v>
+        <v>480971</v>
       </c>
       <c r="R76" t="n">
-        <v>6787507</v>
+        <v>6787547</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8976,17 +8982,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9002,24 +9003,24 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747144</t>
+          <t>https://artportalen.se/Sighting/119568677</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120747368</v>
+        <v>120747144</v>
       </c>
       <c r="B77" t="n">
         <v>79350</v>
@@ -9057,10 +9058,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480840</v>
+        <v>480904</v>
       </c>
       <c r="R77" t="n">
-        <v>6787710</v>
+        <v>6787507</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9097,7 +9098,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9124,13 +9125,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747368</t>
+          <t>https://artportalen.se/Sighting/120747144</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125105944</v>
+        <v>120747368</v>
       </c>
       <c r="B78" t="n">
         <v>79350</v>
@@ -9159,19 +9160,22 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481003</v>
+        <v>480840</v>
       </c>
       <c r="R78" t="n">
-        <v>6787803</v>
+        <v>6787710</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9195,22 +9199,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9219,6 +9218,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9236,16 +9236,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125105944</t>
+          <t>https://artportalen.se/Sighting/120747368</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135710473</v>
+        <v>125105944</v>
       </c>
       <c r="B79" t="n">
-        <v>79477</v>
+        <v>79350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9273,17 +9273,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ekentjärn, Ekentjärn, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480848</v>
+        <v>481003</v>
       </c>
       <c r="R79" t="n">
-        <v>6787635</v>
+        <v>6787803</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9307,27 +9307,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9353,16 +9348,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710473</t>
+          <t>https://artportalen.se/Sighting/125105944</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112989992</v>
+        <v>135710473</v>
       </c>
       <c r="B80" t="n">
-        <v>79359</v>
+        <v>79477</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9370,40 +9365,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>260591</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärn, Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481125</v>
+        <v>480848</v>
       </c>
       <c r="R80" t="n">
-        <v>6787708</v>
+        <v>6787635</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9427,12 +9419,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -9446,7 +9448,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9458,22 +9459,22 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112989992</t>
+          <t>https://artportalen.se/Sighting/135710473</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121972885</v>
+        <v>112989992</v>
       </c>
       <c r="B81" t="n">
-        <v>91909</v>
+        <v>79359</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9481,37 +9482,40 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481124</v>
+        <v>481125</v>
       </c>
       <c r="R81" t="n">
-        <v>6787703</v>
+        <v>6787708</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9535,12 +9539,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9549,55 +9558,56 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972885</t>
+          <t>https://artportalen.se/Sighting/112989992</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121972895</v>
+        <v>121972885</v>
       </c>
       <c r="B82" t="n">
-        <v>93213</v>
+        <v>91909</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9607,10 +9617,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481073</v>
+        <v>481124</v>
       </c>
       <c r="R82" t="n">
-        <v>6787790</v>
+        <v>6787703</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9668,16 +9678,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972895</t>
+          <t>https://artportalen.se/Sighting/121972885</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112996034</v>
+        <v>121972895</v>
       </c>
       <c r="B83" t="n">
-        <v>92281</v>
+        <v>93213</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9685,21 +9695,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9709,10 +9719,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481123</v>
+        <v>481073</v>
       </c>
       <c r="R83" t="n">
-        <v>6787706</v>
+        <v>6787790</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9739,12 +9749,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9759,76 +9769,65 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996034</t>
+          <t>https://artportalen.se/Sighting/121972895</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112996037</v>
+        <v>112996034</v>
       </c>
       <c r="B84" t="n">
-        <v>93197</v>
+        <v>92281</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>2062</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481143</v>
+        <v>481123</v>
       </c>
       <c r="R84" t="n">
-        <v>6787609</v>
+        <v>6787706</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9866,7 +9865,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9884,16 +9882,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996037</t>
+          <t>https://artportalen.se/Sighting/112996034</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112996031</v>
+        <v>112996037</v>
       </c>
       <c r="B85" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9901,26 +9899,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9936,13 +9934,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481063</v>
+        <v>481143</v>
       </c>
       <c r="R85" t="n">
-        <v>6787744</v>
+        <v>6787609</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9980,6 +9978,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9997,16 +9996,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996031</t>
+          <t>https://artportalen.se/Sighting/112996037</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112990060</v>
+        <v>112996031</v>
       </c>
       <c r="B86" t="n">
-        <v>91930</v>
+        <v>93209</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10014,40 +10013,48 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>4366</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481141</v>
+        <v>481063</v>
       </c>
       <c r="R86" t="n">
-        <v>6787582</v>
+        <v>6787744</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10079,83 +10086,80 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112990060</t>
+          <t>https://artportalen.se/Sighting/112996031</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112996032</v>
+        <v>112990060</v>
       </c>
       <c r="B87" t="n">
-        <v>91282</v>
+        <v>91930</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5685</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481080</v>
+        <v>481141</v>
       </c>
       <c r="R87" t="n">
-        <v>6787730</v>
+        <v>6787582</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10187,61 +10191,67 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996032</t>
+          <t>https://artportalen.se/Sighting/112990060</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112996036</v>
+        <v>112996032</v>
       </c>
       <c r="B88" t="n">
-        <v>79327</v>
+        <v>91282</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10251,13 +10261,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481143</v>
+        <v>481080</v>
       </c>
       <c r="R88" t="n">
-        <v>6787598</v>
+        <v>6787730</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10312,59 +10322,51 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996036</t>
+          <t>https://artportalen.se/Sighting/112996032</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112983277</v>
+        <v>112996036</v>
       </c>
       <c r="B89" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481142</v>
+        <v>481143</v>
       </c>
       <c r="R89" t="n">
-        <v>6787700</v>
+        <v>6787598</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10394,19 +10396,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10421,56 +10413,59 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983277</t>
+          <t>https://artportalen.se/Sighting/112996036</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112983978</v>
+        <v>112983277</v>
       </c>
       <c r="B90" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10478,13 +10473,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481104</v>
+        <v>481142</v>
       </c>
       <c r="R90" t="n">
-        <v>6787672</v>
+        <v>6787700</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10513,7 +10508,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10523,7 +10518,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10532,7 +10527,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10544,19 +10538,19 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983978</t>
+          <t>https://artportalen.se/Sighting/112983277</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112996035</v>
+        <v>112983978</v>
       </c>
       <c r="B91" t="n">
         <v>5179</v>
@@ -10588,25 +10582,21 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481128</v>
+        <v>481104</v>
       </c>
       <c r="R91" t="n">
-        <v>6787712</v>
+        <v>6787672</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10633,9 +10623,19 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10651,24 +10651,24 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996035</t>
+          <t>https://artportalen.se/Sighting/112983978</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121972923</v>
+        <v>112996035</v>
       </c>
       <c r="B92" t="n">
         <v>5179</v>
@@ -10697,19 +10697,28 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481148</v>
+        <v>481128</v>
       </c>
       <c r="R92" t="n">
-        <v>6787700</v>
+        <v>6787712</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10733,12 +10742,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10747,33 +10756,34 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972923</t>
+          <t>https://artportalen.se/Sighting/112996035</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121972882</v>
+        <v>121972923</v>
       </c>
       <c r="B93" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10781,21 +10791,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10866,16 +10876,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972882</t>
+          <t>https://artportalen.se/Sighting/121972923</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112983991</v>
+        <v>121972882</v>
       </c>
       <c r="B94" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10883,42 +10893,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481104</v>
+        <v>481148</v>
       </c>
       <c r="R94" t="n">
-        <v>6787672</v>
+        <v>6787700</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10942,22 +10947,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10966,72 +10961,76 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983991</t>
+          <t>https://artportalen.se/Sighting/121972882</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112996033</v>
+        <v>112983991</v>
       </c>
       <c r="B95" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481079</v>
+        <v>481104</v>
       </c>
       <c r="R95" t="n">
-        <v>6787734</v>
+        <v>6787672</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11058,33 +11057,146 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983991</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>112996033</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>481079</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6787734</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112996033</t>
         </is>
@@ -11186,6 +11298,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ96"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121972907</v>
+        <v>136489706</v>
       </c>
       <c r="B44" t="n">
-        <v>93209</v>
+        <v>93399</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5318,21 +5318,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480936</v>
+        <v>481015</v>
       </c>
       <c r="R44" t="n">
-        <v>6787692</v>
+        <v>6787850</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5372,12 +5372,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5392,49 +5402,49 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972907</t>
+          <t>https://artportalen.se/Sighting/136489706</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112996025</v>
+        <v>136489707</v>
       </c>
       <c r="B45" t="n">
-        <v>91893</v>
+        <v>93399</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5444,13 +5454,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480874</v>
+        <v>481006</v>
       </c>
       <c r="R45" t="n">
-        <v>6787479</v>
+        <v>6787842</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5474,12 +5484,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5494,27 +5514,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996025</t>
+          <t>https://artportalen.se/Sighting/136489707</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112996029</v>
+        <v>121972907</v>
       </c>
       <c r="B46" t="n">
-        <v>90522</v>
+        <v>93209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5522,44 +5542,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4962</v>
+        <v>4366</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481007</v>
+        <v>480936</v>
       </c>
       <c r="R46" t="n">
-        <v>6787835</v>
+        <v>6787692</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5583,12 +5596,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5603,68 +5616,65 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996029</t>
+          <t>https://artportalen.se/Sighting/121972907</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112914094</v>
+        <v>112996025</v>
       </c>
       <c r="B47" t="n">
-        <v>91930</v>
+        <v>91893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>4660</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480743</v>
+        <v>480874</v>
       </c>
       <c r="R47" t="n">
-        <v>6787694</v>
+        <v>6787479</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5688,12 +5698,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5702,34 +5712,33 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914094</t>
+          <t>https://artportalen.se/Sighting/112996025</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112923898</v>
+        <v>112996029</v>
       </c>
       <c r="B48" t="n">
-        <v>93223</v>
+        <v>90522</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5737,28 +5746,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5448</v>
+        <v>4962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -5768,14 +5773,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480942</v>
+        <v>481007</v>
       </c>
       <c r="R48" t="n">
-        <v>6787720</v>
+        <v>6787835</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5802,22 +5807,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5826,34 +5821,33 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923898</t>
+          <t>https://artportalen.se/Sighting/112996029</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112996028</v>
+        <v>112914094</v>
       </c>
       <c r="B49" t="n">
-        <v>93235</v>
+        <v>91930</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5861,37 +5855,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480995</v>
+        <v>480743</v>
       </c>
       <c r="R49" t="n">
-        <v>6787829</v>
+        <v>6787694</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5915,12 +5912,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5929,74 +5926,83 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996028</t>
+          <t>https://artportalen.se/Sighting/112914094</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>96117407</v>
+        <v>112923898</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>93223</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480781</v>
+        <v>480942</v>
       </c>
       <c r="R50" t="n">
-        <v>6787572</v>
+        <v>6787720</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6020,12 +6026,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6038,83 +6054,65 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117407</t>
+          <t>https://artportalen.se/Sighting/112923898</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112914136</v>
+        <v>112996028</v>
       </c>
       <c r="B51" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480780</v>
+        <v>480995</v>
       </c>
       <c r="R51" t="n">
-        <v>6787640</v>
+        <v>6787829</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6141,17 +6139,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6160,31 +6153,30 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914136</t>
+          <t>https://artportalen.se/Sighting/112996028</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112923198</v>
+        <v>96117407</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6213,20 +6205,22 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480817</v>
+        <v>480781</v>
       </c>
       <c r="R52" t="n">
-        <v>6787576</v>
+        <v>6787572</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6250,27 +6244,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6279,30 +6258,46 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923198</t>
+          <t>https://artportalen.se/Sighting/96117407</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112923608</v>
+        <v>112914136</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6331,20 +6326,22 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480882</v>
+        <v>480780</v>
       </c>
       <c r="R53" t="n">
-        <v>6787809</v>
+        <v>6787640</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6368,22 +6365,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6392,30 +6384,31 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923608</t>
+          <t>https://artportalen.se/Sighting/112914136</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112924155</v>
+        <v>112923198</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6451,13 +6444,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480927</v>
+        <v>480817</v>
       </c>
       <c r="R54" t="n">
-        <v>6787699</v>
+        <v>6787576</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6486,7 +6479,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6496,7 +6489,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6522,13 +6520,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924155</t>
+          <t>https://artportalen.se/Sighting/112923198</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120747170</v>
+        <v>112923608</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6557,19 +6555,17 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480886</v>
+        <v>480882</v>
       </c>
       <c r="R55" t="n">
-        <v>6787539</v>
+        <v>6787809</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6596,17 +6592,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6615,31 +6616,30 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747170</t>
+          <t>https://artportalen.se/Sighting/112923608</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120747198</v>
+        <v>112924155</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6668,22 +6668,20 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480878</v>
+        <v>480927</v>
       </c>
       <c r="R56" t="n">
-        <v>6787512</v>
+        <v>6787699</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6707,17 +6705,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6726,31 +6729,30 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747198</t>
+          <t>https://artportalen.se/Sighting/112924155</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120747228</v>
+        <v>120747170</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6788,10 +6790,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480890</v>
+        <v>480886</v>
       </c>
       <c r="R57" t="n">
-        <v>6787571</v>
+        <v>6787539</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6855,13 +6857,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747228</t>
+          <t>https://artportalen.se/Sighting/120747170</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120747402</v>
+        <v>120747198</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -6899,10 +6901,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480831</v>
+        <v>480878</v>
       </c>
       <c r="R58" t="n">
-        <v>6787737</v>
+        <v>6787512</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6966,54 +6968,57 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747402</t>
+          <t>https://artportalen.se/Sighting/120747198</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112996022</v>
+        <v>120747228</v>
       </c>
       <c r="B59" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480891</v>
+        <v>480890</v>
       </c>
       <c r="R59" t="n">
-        <v>6787557</v>
+        <v>6787571</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7037,12 +7042,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7051,77 +7061,75 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996022</t>
+          <t>https://artportalen.se/Sighting/120747228</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112924074</v>
+        <v>120747402</v>
       </c>
       <c r="B60" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481017</v>
+        <v>480831</v>
       </c>
       <c r="R60" t="n">
-        <v>6787651</v>
+        <v>6787737</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,22 +7153,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7169,33 +7172,34 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924074</t>
+          <t>https://artportalen.se/Sighting/120747402</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112980896</v>
+        <v>112996022</v>
       </c>
       <c r="B61" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7203,43 +7207,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480919</v>
+        <v>480891</v>
       </c>
       <c r="R61" t="n">
-        <v>6787525</v>
+        <v>6787557</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7266,19 +7264,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:39</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7293,24 +7281,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112980896</t>
+          <t>https://artportalen.se/Sighting/112996022</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125106308</v>
+        <v>112924074</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -7339,19 +7327,25 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480781</v>
+        <v>481017</v>
       </c>
       <c r="R62" t="n">
-        <v>6787572</v>
+        <v>6787651</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7375,27 +7369,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Hackmärken färska i gran</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7410,27 +7399,27 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125106308</t>
+          <t>https://artportalen.se/Sighting/112924074</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112923064</v>
+        <v>112980896</v>
       </c>
       <c r="B63" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7438,32 +7427,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7472,13 +7457,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480817</v>
+        <v>480919</v>
       </c>
       <c r="R63" t="n">
-        <v>6787576</v>
+        <v>6787525</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7502,22 +7487,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7543,16 +7528,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923064</t>
+          <t>https://artportalen.se/Sighting/112980896</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112982228</v>
+        <v>125106308</v>
       </c>
       <c r="B64" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7560,41 +7545,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480787</v>
+        <v>480781</v>
       </c>
       <c r="R64" t="n">
-        <v>6787755</v>
+        <v>6787572</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7618,22 +7599,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Hackmärken färska i gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7648,56 +7634,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112982228</t>
+          <t>https://artportalen.se/Sighting/125106308</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112923140</v>
+        <v>112923064</v>
       </c>
       <c r="B65" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7712,7 +7702,7 @@
         <v>6787576</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7741,7 +7731,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7751,7 +7741,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7777,60 +7767,58 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923140</t>
+          <t>https://artportalen.se/Sighting/112923064</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112923512</v>
+        <v>112982228</v>
       </c>
       <c r="B66" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480733</v>
+        <v>480787</v>
       </c>
       <c r="R66" t="n">
-        <v>6787668</v>
+        <v>6787755</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7854,22 +7842,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7889,19 +7877,19 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923512</t>
+          <t>https://artportalen.se/Sighting/112982228</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112924028</v>
+        <v>112923140</v>
       </c>
       <c r="B67" t="n">
         <v>8455</v>
@@ -7931,19 +7919,24 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481017</v>
+        <v>480817</v>
       </c>
       <c r="R67" t="n">
-        <v>6787651</v>
+        <v>6787576</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7972,7 +7965,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7982,7 +7975,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8008,13 +8001,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924028</t>
+          <t>https://artportalen.se/Sighting/112923140</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112924151</v>
+        <v>112923512</v>
       </c>
       <c r="B68" t="n">
         <v>8455</v>
@@ -8044,19 +8037,24 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480927</v>
+        <v>480733</v>
       </c>
       <c r="R68" t="n">
-        <v>6787699</v>
+        <v>6787668</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8085,7 +8083,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8095,7 +8093,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8121,13 +8119,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924151</t>
+          <t>https://artportalen.se/Sighting/112923512</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120747281</v>
+        <v>112924028</v>
       </c>
       <c r="B69" t="n">
         <v>8455</v>
@@ -8156,24 +8154,20 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480845</v>
+        <v>481017</v>
       </c>
       <c r="R69" t="n">
-        <v>6787659</v>
+        <v>6787651</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8197,17 +8191,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8216,31 +8215,30 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747281</t>
+          <t>https://artportalen.se/Sighting/112924028</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120747340</v>
+        <v>112924151</v>
       </c>
       <c r="B70" t="n">
         <v>8455</v>
@@ -8269,24 +8267,20 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480847</v>
+        <v>480927</v>
       </c>
       <c r="R70" t="n">
-        <v>6787707</v>
+        <v>6787699</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8310,17 +8304,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8329,34 +8328,33 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747340</t>
+          <t>https://artportalen.se/Sighting/112924151</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135708300</v>
+        <v>120747281</v>
       </c>
       <c r="B71" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8382,24 +8380,24 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480839</v>
+        <v>480845</v>
       </c>
       <c r="R71" t="n">
-        <v>6787636</v>
+        <v>6787659</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8423,22 +8421,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>08:59</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>08:59</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8447,18 +8440,9 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8474,63 +8458,56 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708300</t>
+          <t>https://artportalen.se/Sighting/120747281</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119568643</v>
+        <v>120747340</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481007</v>
+        <v>480847</v>
       </c>
       <c r="R72" t="n">
-        <v>6787620</v>
+        <v>6787707</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8557,12 +8534,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8578,27 +8560,27 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568643</t>
+          <t>https://artportalen.se/Sighting/120747340</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125187193</v>
+        <v>135708300</v>
       </c>
       <c r="B73" t="n">
-        <v>104628</v>
+        <v>8463</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8606,43 +8588,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222412</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480717</v>
+        <v>480839</v>
       </c>
       <c r="R73" t="n">
-        <v>6787597</v>
+        <v>6787636</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8669,12 +8647,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8685,66 +8673,88 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125187193</t>
+          <t>https://artportalen.se/Sighting/135708300</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112996021</v>
+        <v>119568643</v>
       </c>
       <c r="B74" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480899</v>
+        <v>481007</v>
       </c>
       <c r="R74" t="n">
-        <v>6787538</v>
+        <v>6787620</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8771,12 +8781,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8785,71 +8795,81 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996021</t>
+          <t>https://artportalen.se/Sighting/119568643</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121972913</v>
+        <v>125187193</v>
       </c>
       <c r="B75" t="n">
-        <v>79085</v>
+        <v>104628</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>222412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480935</v>
+        <v>480717</v>
       </c>
       <c r="R75" t="n">
-        <v>6787807</v>
+        <v>6787597</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8873,12 +8893,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8893,27 +8913,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972913</t>
+          <t>https://artportalen.se/Sighting/125187193</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119568677</v>
+        <v>112996021</v>
       </c>
       <c r="B76" t="n">
-        <v>91402</v>
+        <v>79085</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8921,41 +8941,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>256703</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480971</v>
+        <v>480899</v>
       </c>
       <c r="R76" t="n">
-        <v>6787547</v>
+        <v>6787538</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8982,12 +8995,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8996,34 +9009,33 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568677</t>
+          <t>https://artportalen.se/Sighting/112996021</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120747144</v>
+        <v>121972913</v>
       </c>
       <c r="B77" t="n">
-        <v>79350</v>
+        <v>79085</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9031,37 +9043,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480904</v>
+        <v>480935</v>
       </c>
       <c r="R77" t="n">
-        <v>6787507</v>
+        <v>6787807</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9088,17 +9097,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9107,34 +9111,33 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747144</t>
+          <t>https://artportalen.se/Sighting/121972913</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120747368</v>
+        <v>119568677</v>
       </c>
       <c r="B78" t="n">
-        <v>79350</v>
+        <v>91402</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9142,37 +9145,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>260591</v>
+        <v>256703</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480840</v>
+        <v>480971</v>
       </c>
       <c r="R78" t="n">
-        <v>6787710</v>
+        <v>6787547</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9199,17 +9206,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>på tall</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9225,24 +9227,24 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747368</t>
+          <t>https://artportalen.se/Sighting/119568677</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125105944</v>
+        <v>120747144</v>
       </c>
       <c r="B79" t="n">
         <v>79350</v>
@@ -9271,19 +9273,22 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481003</v>
+        <v>480904</v>
       </c>
       <c r="R79" t="n">
-        <v>6787803</v>
+        <v>6787507</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9307,22 +9312,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9331,6 +9331,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9348,16 +9349,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125105944</t>
+          <t>https://artportalen.se/Sighting/120747144</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135710473</v>
+        <v>120747368</v>
       </c>
       <c r="B80" t="n">
-        <v>79477</v>
+        <v>79350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9383,16 +9384,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ekentjärn, Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480848</v>
+        <v>480840</v>
       </c>
       <c r="R80" t="n">
-        <v>6787635</v>
+        <v>6787710</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9419,27 +9423,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9448,6 +9442,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9465,16 +9460,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710473</t>
+          <t>https://artportalen.se/Sighting/120747368</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112989992</v>
+        <v>125105944</v>
       </c>
       <c r="B81" t="n">
-        <v>79359</v>
+        <v>79350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9482,37 +9477,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>260591</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481125</v>
+        <v>481003</v>
       </c>
       <c r="R81" t="n">
-        <v>6787708</v>
+        <v>6787803</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9539,17 +9531,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9558,7 +9555,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9570,22 +9566,22 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112989992</t>
+          <t>https://artportalen.se/Sighting/125105944</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121972885</v>
+        <v>135710473</v>
       </c>
       <c r="B82" t="n">
-        <v>91909</v>
+        <v>79477</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9593,34 +9589,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>260591</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481124</v>
+        <v>480848</v>
       </c>
       <c r="R82" t="n">
-        <v>6787703</v>
+        <v>6787635</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9647,12 +9643,27 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9667,65 +9678,68 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972885</t>
+          <t>https://artportalen.se/Sighting/135710473</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121972895</v>
+        <v>112989992</v>
       </c>
       <c r="B83" t="n">
-        <v>93213</v>
+        <v>79359</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2059</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481073</v>
+        <v>481125</v>
       </c>
       <c r="R83" t="n">
-        <v>6787790</v>
+        <v>6787708</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9749,12 +9763,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9763,55 +9782,56 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972895</t>
+          <t>https://artportalen.se/Sighting/112989992</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112996034</v>
+        <v>121972885</v>
       </c>
       <c r="B84" t="n">
-        <v>92281</v>
+        <v>91909</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9821,10 +9841,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481123</v>
+        <v>481124</v>
       </c>
       <c r="R84" t="n">
-        <v>6787706</v>
+        <v>6787703</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9851,12 +9871,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9871,76 +9891,65 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996034</t>
+          <t>https://artportalen.se/Sighting/121972885</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112996037</v>
+        <v>121972895</v>
       </c>
       <c r="B85" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481143</v>
+        <v>481073</v>
       </c>
       <c r="R85" t="n">
-        <v>6787609</v>
+        <v>6787790</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9964,12 +9973,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9978,83 +9987,71 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996037</t>
+          <t>https://artportalen.se/Sighting/121972895</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112996031</v>
+        <v>112996034</v>
       </c>
       <c r="B86" t="n">
-        <v>93209</v>
+        <v>92281</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4366</v>
+        <v>2062</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481063</v>
+        <v>481123</v>
       </c>
       <c r="R86" t="n">
-        <v>6787744</v>
+        <v>6787706</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10109,16 +10106,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996031</t>
+          <t>https://artportalen.se/Sighting/112996034</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112990060</v>
+        <v>112996037</v>
       </c>
       <c r="B87" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10126,37 +10123,45 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481141</v>
+        <v>481143</v>
       </c>
       <c r="R87" t="n">
-        <v>6787582</v>
+        <v>6787609</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10191,11 +10196,6 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10209,62 +10209,73 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112990060</t>
+          <t>https://artportalen.se/Sighting/112996037</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112996032</v>
+        <v>112996031</v>
       </c>
       <c r="B88" t="n">
-        <v>91282</v>
+        <v>93209</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5685</v>
+        <v>4366</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481080</v>
+        <v>481063</v>
       </c>
       <c r="R88" t="n">
-        <v>6787730</v>
+        <v>6787744</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10322,51 +10333,54 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996032</t>
+          <t>https://artportalen.se/Sighting/112996031</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112996036</v>
+        <v>112990060</v>
       </c>
       <c r="B89" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481143</v>
+        <v>481141</v>
       </c>
       <c r="R89" t="n">
-        <v>6787598</v>
+        <v>6787582</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10401,85 +10415,83 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996036</t>
+          <t>https://artportalen.se/Sighting/112990060</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112983277</v>
+        <v>112996032</v>
       </c>
       <c r="B90" t="n">
-        <v>57953</v>
+        <v>91282</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481142</v>
+        <v>481080</v>
       </c>
       <c r="R90" t="n">
-        <v>6787700</v>
+        <v>6787730</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10506,19 +10518,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10533,70 +10535,65 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983277</t>
+          <t>https://artportalen.se/Sighting/112996032</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112983978</v>
+        <v>112996036</v>
       </c>
       <c r="B91" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481104</v>
+        <v>481143</v>
       </c>
       <c r="R91" t="n">
-        <v>6787672</v>
+        <v>6787598</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10623,99 +10620,87 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983978</t>
+          <t>https://artportalen.se/Sighting/112996036</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112996035</v>
+        <v>112983277</v>
       </c>
       <c r="B92" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481128</v>
+        <v>481142</v>
       </c>
       <c r="R92" t="n">
-        <v>6787712</v>
+        <v>6787700</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10745,42 +10730,51 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996035</t>
+          <t>https://artportalen.se/Sighting/112983277</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121972923</v>
+        <v>112983978</v>
       </c>
       <c r="B93" t="n">
         <v>5179</v>
@@ -10809,16 +10803,21 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>481148</v>
+        <v>481104</v>
       </c>
       <c r="R93" t="n">
-        <v>6787700</v>
+        <v>6787672</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10845,12 +10844,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10859,33 +10868,34 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972923</t>
+          <t>https://artportalen.se/Sighting/112983978</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121972882</v>
+        <v>112996035</v>
       </c>
       <c r="B94" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10893,37 +10903,46 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481148</v>
+        <v>481128</v>
       </c>
       <c r="R94" t="n">
-        <v>6787700</v>
+        <v>6787712</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10947,12 +10966,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10961,33 +10980,34 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972882</t>
+          <t>https://artportalen.se/Sighting/112996035</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112983991</v>
+        <v>121972923</v>
       </c>
       <c r="B95" t="n">
-        <v>8455</v>
+        <v>5179</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10995,42 +11015,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481104</v>
+        <v>481148</v>
       </c>
       <c r="R95" t="n">
-        <v>6787672</v>
+        <v>6787700</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11054,22 +11069,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11078,56 +11083,55 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983991</t>
+          <t>https://artportalen.se/Sighting/121972923</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112996033</v>
+        <v>121972882</v>
       </c>
       <c r="B96" t="n">
-        <v>79085</v>
+        <v>5199</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>105930</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11137,10 +11141,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481079</v>
+        <v>481148</v>
       </c>
       <c r="R96" t="n">
-        <v>6787734</v>
+        <v>6787700</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11167,12 +11171,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11187,16 +11191,236 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972882</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>112983991</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>481104</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6787672</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983991</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>112996033</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>481079</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6787734</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112996033</t>
         </is>
@@ -11299,6 +11523,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -2568,7 +2568,7 @@
         <v>136457415</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>136489706</v>
       </c>
       <c r="B44" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>136489707</v>
       </c>
       <c r="B45" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
